--- a/research/traditional_assets/database/data/norway/norway_transportation.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_transportation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ob_tre" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,59 +589,77 @@
           <t>Transportation</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.396</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0.9970887918486171</v>
+      </c>
+      <c r="J2">
+        <v>0.9471598314197253</v>
+      </c>
       <c r="K2">
-        <v>-182.3</v>
+        <v>63.5</v>
+      </c>
+      <c r="L2">
+        <v>0.9243085880640466</v>
       </c>
       <c r="M2">
-        <v>33.8</v>
+        <v>16.31</v>
       </c>
       <c r="N2">
-        <v>0.0924507658643326</v>
+        <v>0.03828638497652583</v>
       </c>
       <c r="O2">
-        <v>-0.1854086670323642</v>
+        <v>0.2568503937007874</v>
       </c>
       <c r="P2">
-        <v>22.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q2">
-        <v>0.06236323851203501</v>
+        <v>0.02676056338028169</v>
       </c>
       <c r="R2">
-        <v>-0.1250685682940209</v>
+        <v>0.1795275590551181</v>
       </c>
       <c r="S2">
-        <v>11</v>
+        <v>4.910000000000002</v>
       </c>
       <c r="T2">
-        <v>0.3254437869822485</v>
+        <v>0.3010423053341509</v>
       </c>
       <c r="U2">
-        <v>13.5</v>
+        <v>12.1</v>
       </c>
       <c r="V2">
-        <v>0.03692560175054704</v>
+        <v>0.0284037558685446</v>
       </c>
       <c r="W2">
-        <v>-0.2275053038811931</v>
+        <v>0.1087514985442713</v>
       </c>
       <c r="X2">
-        <v>0.08817657813711355</v>
+        <v>0.07651309815625496</v>
       </c>
       <c r="Y2">
-        <v>-0.3156818820183066</v>
+        <v>0.03223840038801633</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.1204417952314166</v>
       </c>
       <c r="AA2">
-        <v>-0.2359256349829798</v>
+        <v>0.1140776304672776</v>
       </c>
       <c r="AB2">
-        <v>0.08817657813711355</v>
+        <v>0.07651309815625496</v>
       </c>
       <c r="AC2">
-        <v>-0.3241022131200934</v>
+        <v>0.03756453231102264</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -651,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-13.5</v>
+        <v>-12.1</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -660,22 +680,22 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03834138028969043</v>
+        <v>-0.02923411452041556</v>
       </c>
       <c r="AK2">
-        <v>-0.02366760168302945</v>
+        <v>-0.01955397543632838</v>
       </c>
       <c r="AL2">
-        <v>0.077</v>
+        <v>0.106</v>
       </c>
       <c r="AM2">
-        <v>0.077</v>
+        <v>0.106</v>
       </c>
       <c r="AO2">
-        <v>-2340.25974025974</v>
+        <v>646.2264150943396</v>
       </c>
       <c r="AQ2">
-        <v>-2340.25974025974</v>
+        <v>646.2264150943396</v>
       </c>
     </row>
     <row r="3">
@@ -694,59 +714,77 @@
           <t>Transportation</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.396</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.9970887918486171</v>
+      </c>
+      <c r="J3">
+        <v>0.9471598314197253</v>
+      </c>
       <c r="K3">
-        <v>-182.3</v>
+        <v>63.5</v>
+      </c>
+      <c r="L3">
+        <v>0.9243085880640466</v>
       </c>
       <c r="M3">
-        <v>33.8</v>
+        <v>16.31</v>
       </c>
       <c r="N3">
-        <v>0.0924507658643326</v>
+        <v>0.03828638497652583</v>
       </c>
       <c r="O3">
-        <v>-0.1854086670323642</v>
+        <v>0.2568503937007874</v>
       </c>
       <c r="P3">
-        <v>22.8</v>
+        <v>11.4</v>
       </c>
       <c r="Q3">
-        <v>0.06236323851203501</v>
+        <v>0.02676056338028169</v>
       </c>
       <c r="R3">
-        <v>-0.1250685682940209</v>
+        <v>0.1795275590551181</v>
       </c>
       <c r="S3">
-        <v>11</v>
+        <v>4.910000000000002</v>
       </c>
       <c r="T3">
-        <v>0.3254437869822485</v>
+        <v>0.3010423053341509</v>
       </c>
       <c r="U3">
-        <v>13.5</v>
+        <v>12.1</v>
       </c>
       <c r="V3">
-        <v>0.03692560175054704</v>
+        <v>0.0284037558685446</v>
       </c>
       <c r="W3">
-        <v>-0.2275053038811931</v>
+        <v>0.1087514985442713</v>
       </c>
       <c r="X3">
-        <v>0.08817657813711355</v>
+        <v>0.07651309815625496</v>
       </c>
       <c r="Y3">
-        <v>-0.3156818820183066</v>
+        <v>0.03223840038801633</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.1204417952314166</v>
       </c>
       <c r="AA3">
-        <v>-0.2359256349829798</v>
+        <v>0.1140776304672776</v>
       </c>
       <c r="AB3">
-        <v>0.08817657813711355</v>
+        <v>0.07651309815625496</v>
       </c>
       <c r="AC3">
-        <v>-0.3241022131200934</v>
+        <v>0.03756453231102264</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -758,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-13.5</v>
+        <v>-12.1</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -767,22 +805,8793 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.03834138028969043</v>
+        <v>-0.02923411452041556</v>
       </c>
       <c r="AK3">
-        <v>-0.02366760168302945</v>
+        <v>-0.01955397543632838</v>
       </c>
       <c r="AL3">
-        <v>0.077</v>
+        <v>0.106</v>
       </c>
       <c r="AM3">
-        <v>0.077</v>
+        <v>0.106</v>
       </c>
       <c r="AO3">
-        <v>-2340.25974025974</v>
+        <v>646.2264150943396</v>
       </c>
       <c r="AQ3">
-        <v>-2340.25974025974</v>
+        <v>646.2264150943396</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasure ASA (OB:TRE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OB:TRE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>646.22641509434</v>
+      </c>
+      <c r="F2">
+        <v>4.51299809334066</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.7</v>
+      </c>
+      <c r="K2">
+        <v>426</v>
+      </c>
+      <c r="L2">
+        <v>145.972079859809</v>
+      </c>
+      <c r="M2">
+        <v>413.9</v>
+      </c>
+      <c r="N2">
+        <v>432.072079859809</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>298.2</v>
+      </c>
+      <c r="Q2">
+        <v>0.076513098156255</v>
+      </c>
+      <c r="R2">
+        <v>0.0713366810401917</v>
+      </c>
+      <c r="S2">
+        <v>0.03513354</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.076513098156255</v>
+      </c>
+      <c r="X2">
+        <v>0.145150936800639</v>
+      </c>
+      <c r="Y2">
+        <v>0.819849959918586</v>
+      </c>
+      <c r="Z2">
+        <v>2.31197688697041</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0.045043</v>
+      </c>
+      <c r="AC2">
+        <v>646.2264150943396</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0.106</v>
+      </c>
+      <c r="AF2">
+        <v>-68.5</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>426</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>-68.5</v>
+      </c>
+      <c r="AR2">
+        <v>0.106</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>12.1</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07651309815625496</v>
+      </c>
+      <c r="C2">
+        <v>426</v>
+      </c>
+      <c r="D2">
+        <v>413.9</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>12.1</v>
+      </c>
+      <c r="H2">
+        <v>426</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>-68.5</v>
+      </c>
+      <c r="L2">
+        <v>68.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>68.5</v>
+      </c>
+      <c r="O2">
+        <v>15.07</v>
+      </c>
+      <c r="P2">
+        <v>53.43</v>
+      </c>
+      <c r="Q2">
+        <v>-15.07</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07651309815625496</v>
+      </c>
+      <c r="T2">
+        <v>0.8198499599185859</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07639078934031118</v>
+      </c>
+      <c r="C3">
+        <v>422.1517220736583</v>
+      </c>
+      <c r="D3">
+        <v>414.3117220736582</v>
+      </c>
+      <c r="E3">
+        <v>4.26</v>
+      </c>
+      <c r="F3">
+        <v>4.26</v>
+      </c>
+      <c r="G3">
+        <v>12.1</v>
+      </c>
+      <c r="H3">
+        <v>426</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>-68.5</v>
+      </c>
+      <c r="L3">
+        <v>68.5</v>
+      </c>
+      <c r="M3">
+        <v>0.190422</v>
+      </c>
+      <c r="N3">
+        <v>68.309578</v>
+      </c>
+      <c r="O3">
+        <v>15.02810716</v>
+      </c>
+      <c r="P3">
+        <v>53.28147084</v>
+      </c>
+      <c r="Q3">
+        <v>-15.21852916</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07681023165687999</v>
+      </c>
+      <c r="T3">
+        <v>0.8263093838452171</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.034866</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>359.727342428921</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07626848052436742</v>
+      </c>
+      <c r="C4">
+        <v>418.304264074144</v>
+      </c>
+      <c r="D4">
+        <v>414.7242640741439</v>
+      </c>
+      <c r="E4">
+        <v>8.52</v>
+      </c>
+      <c r="F4">
+        <v>8.52</v>
+      </c>
+      <c r="G4">
+        <v>12.1</v>
+      </c>
+      <c r="H4">
+        <v>426</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>-68.5</v>
+      </c>
+      <c r="L4">
+        <v>68.5</v>
+      </c>
+      <c r="M4">
+        <v>0.380844</v>
+      </c>
+      <c r="N4">
+        <v>68.119156</v>
+      </c>
+      <c r="O4">
+        <v>14.98621432</v>
+      </c>
+      <c r="P4">
+        <v>53.13294168</v>
+      </c>
+      <c r="Q4">
+        <v>-15.36705832</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07711342910649738</v>
+      </c>
+      <c r="T4">
+        <v>0.832900632749943</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.034866</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>179.8636712144605</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07614617170842367</v>
+      </c>
+      <c r="C5">
+        <v>414.4576284531718</v>
+      </c>
+      <c r="D5">
+        <v>415.1376284531718</v>
+      </c>
+      <c r="E5">
+        <v>12.78</v>
+      </c>
+      <c r="F5">
+        <v>12.78</v>
+      </c>
+      <c r="G5">
+        <v>12.1</v>
+      </c>
+      <c r="H5">
+        <v>426</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>-68.5</v>
+      </c>
+      <c r="L5">
+        <v>68.5</v>
+      </c>
+      <c r="M5">
+        <v>0.5712660000000001</v>
+      </c>
+      <c r="N5">
+        <v>67.92873400000001</v>
+      </c>
+      <c r="O5">
+        <v>14.94432148</v>
+      </c>
+      <c r="P5">
+        <v>52.98441252000001</v>
+      </c>
+      <c r="Q5">
+        <v>-15.51558747999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.0774228780499213</v>
+      </c>
+      <c r="T5">
+        <v>0.8396277836939414</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.034866</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>119.9091141429737</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07602386289247991</v>
+      </c>
+      <c r="C6">
+        <v>410.6118176722411</v>
+      </c>
+      <c r="D6">
+        <v>415.5518176722411</v>
+      </c>
+      <c r="E6">
+        <v>17.04</v>
+      </c>
+      <c r="F6">
+        <v>17.04</v>
+      </c>
+      <c r="G6">
+        <v>12.1</v>
+      </c>
+      <c r="H6">
+        <v>426</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-68.5</v>
+      </c>
+      <c r="L6">
+        <v>68.5</v>
+      </c>
+      <c r="M6">
+        <v>0.761688</v>
+      </c>
+      <c r="N6">
+        <v>67.73831199999999</v>
+      </c>
+      <c r="O6">
+        <v>14.90242864</v>
+      </c>
+      <c r="P6">
+        <v>52.83588336</v>
+      </c>
+      <c r="Q6">
+        <v>-15.66411664</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.07773877384633324</v>
+      </c>
+      <c r="T6">
+        <v>0.8464950836159399</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.034866</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>89.93183560723024</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07590155407653615</v>
+      </c>
+      <c r="C7">
+        <v>406.7668342026845</v>
+      </c>
+      <c r="D7">
+        <v>415.9668342026845</v>
+      </c>
+      <c r="E7">
+        <v>21.3</v>
+      </c>
+      <c r="F7">
+        <v>21.3</v>
+      </c>
+      <c r="G7">
+        <v>12.1</v>
+      </c>
+      <c r="H7">
+        <v>426</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-68.5</v>
+      </c>
+      <c r="L7">
+        <v>68.5</v>
+      </c>
+      <c r="M7">
+        <v>0.9521100000000001</v>
+      </c>
+      <c r="N7">
+        <v>67.54789</v>
+      </c>
+      <c r="O7">
+        <v>14.8605358</v>
+      </c>
+      <c r="P7">
+        <v>52.68735419999999</v>
+      </c>
+      <c r="Q7">
+        <v>-15.81264580000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07806132008056436</v>
+      </c>
+      <c r="T7">
+        <v>0.8535069582731384</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.034866</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>71.94546848578419</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07577924526059239</v>
+      </c>
+      <c r="C8">
+        <v>402.9226805257171</v>
+      </c>
+      <c r="D8">
+        <v>416.3826805257171</v>
+      </c>
+      <c r="E8">
+        <v>25.56</v>
+      </c>
+      <c r="F8">
+        <v>25.56</v>
+      </c>
+      <c r="G8">
+        <v>12.1</v>
+      </c>
+      <c r="H8">
+        <v>426</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-68.5</v>
+      </c>
+      <c r="L8">
+        <v>68.5</v>
+      </c>
+      <c r="M8">
+        <v>1.142532</v>
+      </c>
+      <c r="N8">
+        <v>67.357468</v>
+      </c>
+      <c r="O8">
+        <v>14.81864296</v>
+      </c>
+      <c r="P8">
+        <v>52.53882504</v>
+      </c>
+      <c r="Q8">
+        <v>-15.96117496</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0783907290006302</v>
+      </c>
+      <c r="T8">
+        <v>0.8606680217528303</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.034866</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>59.95455707148683</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07565693644464865</v>
+      </c>
+      <c r="C9">
+        <v>399.0793591324859</v>
+      </c>
+      <c r="D9">
+        <v>416.7993591324858</v>
+      </c>
+      <c r="E9">
+        <v>29.82</v>
+      </c>
+      <c r="F9">
+        <v>29.82</v>
+      </c>
+      <c r="G9">
+        <v>12.1</v>
+      </c>
+      <c r="H9">
+        <v>426</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>-68.5</v>
+      </c>
+      <c r="L9">
+        <v>68.5</v>
+      </c>
+      <c r="M9">
+        <v>1.332954</v>
+      </c>
+      <c r="N9">
+        <v>67.167046</v>
+      </c>
+      <c r="O9">
+        <v>14.77675012</v>
+      </c>
+      <c r="P9">
+        <v>52.39029588</v>
+      </c>
+      <c r="Q9">
+        <v>-16.10970412</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07872722198349316</v>
+      </c>
+      <c r="T9">
+        <v>0.8679830865976772</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.034866</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>51.38962034698871</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07553462762870487</v>
+      </c>
+      <c r="C10">
+        <v>395.2368725241195</v>
+      </c>
+      <c r="D10">
+        <v>417.2168725241195</v>
+      </c>
+      <c r="E10">
+        <v>34.08</v>
+      </c>
+      <c r="F10">
+        <v>34.08</v>
+      </c>
+      <c r="G10">
+        <v>12.1</v>
+      </c>
+      <c r="H10">
+        <v>426</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>-68.5</v>
+      </c>
+      <c r="L10">
+        <v>68.5</v>
+      </c>
+      <c r="M10">
+        <v>1.523376</v>
+      </c>
+      <c r="N10">
+        <v>66.976624</v>
+      </c>
+      <c r="O10">
+        <v>14.73485728</v>
+      </c>
+      <c r="P10">
+        <v>52.24176672</v>
+      </c>
+      <c r="Q10">
+        <v>-16.25823328</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07907103003120095</v>
+      </c>
+      <c r="T10">
+        <v>0.8754571745913248</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.034866</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>44.96591780361513</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07541231881276111</v>
+      </c>
+      <c r="C11">
+        <v>391.3952232117783</v>
+      </c>
+      <c r="D11">
+        <v>417.6352232117783</v>
+      </c>
+      <c r="E11">
+        <v>38.34</v>
+      </c>
+      <c r="F11">
+        <v>38.34</v>
+      </c>
+      <c r="G11">
+        <v>12.1</v>
+      </c>
+      <c r="H11">
+        <v>426</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-68.5</v>
+      </c>
+      <c r="L11">
+        <v>68.5</v>
+      </c>
+      <c r="M11">
+        <v>1.713798</v>
+      </c>
+      <c r="N11">
+        <v>66.786202</v>
+      </c>
+      <c r="O11">
+        <v>14.69296444</v>
+      </c>
+      <c r="P11">
+        <v>52.09323756000001</v>
+      </c>
+      <c r="Q11">
+        <v>-16.40676243999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07942239429973748</v>
+      </c>
+      <c r="T11">
+        <v>0.8830955282551626</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.034866</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>39.96970471432456</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07529000999681736</v>
+      </c>
+      <c r="C12">
+        <v>387.5544137167046</v>
+      </c>
+      <c r="D12">
+        <v>418.0544137167046</v>
+      </c>
+      <c r="E12">
+        <v>42.6</v>
+      </c>
+      <c r="F12">
+        <v>42.6</v>
+      </c>
+      <c r="G12">
+        <v>12.1</v>
+      </c>
+      <c r="H12">
+        <v>426</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-68.5</v>
+      </c>
+      <c r="L12">
+        <v>68.5</v>
+      </c>
+      <c r="M12">
+        <v>1.90422</v>
+      </c>
+      <c r="N12">
+        <v>66.59578</v>
+      </c>
+      <c r="O12">
+        <v>14.6510716</v>
+      </c>
+      <c r="P12">
+        <v>51.9447084</v>
+      </c>
+      <c r="Q12">
+        <v>-16.5552916</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07978156666313038</v>
+      </c>
+      <c r="T12">
+        <v>0.89090362311153</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.034866</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>35.9727342428921</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07516770118087357</v>
+      </c>
+      <c r="C13">
+        <v>383.7144465702735</v>
+      </c>
+      <c r="D13">
+        <v>418.4744465702735</v>
+      </c>
+      <c r="E13">
+        <v>46.86</v>
+      </c>
+      <c r="F13">
+        <v>46.86</v>
+      </c>
+      <c r="G13">
+        <v>12.1</v>
+      </c>
+      <c r="H13">
+        <v>426</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>-68.5</v>
+      </c>
+      <c r="L13">
+        <v>68.5</v>
+      </c>
+      <c r="M13">
+        <v>2.094642</v>
+      </c>
+      <c r="N13">
+        <v>66.40535800000001</v>
+      </c>
+      <c r="O13">
+        <v>14.60917876</v>
+      </c>
+      <c r="P13">
+        <v>51.79617924000001</v>
+      </c>
+      <c r="Q13">
+        <v>-16.70382075999999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08014881031558829</v>
+      </c>
+      <c r="T13">
+        <v>0.8988871807736587</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.034866</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>32.70248567535646</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07504539236492982</v>
+      </c>
+      <c r="C14">
+        <v>379.8753243140439</v>
+      </c>
+      <c r="D14">
+        <v>418.8953243140439</v>
+      </c>
+      <c r="E14">
+        <v>51.12</v>
+      </c>
+      <c r="F14">
+        <v>51.12</v>
+      </c>
+      <c r="G14">
+        <v>12.1</v>
+      </c>
+      <c r="H14">
+        <v>426</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-68.5</v>
+      </c>
+      <c r="L14">
+        <v>68.5</v>
+      </c>
+      <c r="M14">
+        <v>2.285064</v>
+      </c>
+      <c r="N14">
+        <v>66.21493599999999</v>
+      </c>
+      <c r="O14">
+        <v>14.56728592</v>
+      </c>
+      <c r="P14">
+        <v>51.64765008</v>
+      </c>
+      <c r="Q14">
+        <v>-16.85234992</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08052440041469298</v>
+      </c>
+      <c r="T14">
+        <v>0.9070521829281083</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.034866</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>29.97727853574341</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07492308354898605</v>
+      </c>
+      <c r="C15">
+        <v>376.0370494998094</v>
+      </c>
+      <c r="D15">
+        <v>419.3170494998093</v>
+      </c>
+      <c r="E15">
+        <v>55.38</v>
+      </c>
+      <c r="F15">
+        <v>55.38</v>
+      </c>
+      <c r="G15">
+        <v>12.1</v>
+      </c>
+      <c r="H15">
+        <v>426</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>-68.5</v>
+      </c>
+      <c r="L15">
+        <v>68.5</v>
+      </c>
+      <c r="M15">
+        <v>2.475486000000001</v>
+      </c>
+      <c r="N15">
+        <v>66.024514</v>
+      </c>
+      <c r="O15">
+        <v>14.52539308</v>
+      </c>
+      <c r="P15">
+        <v>51.49912092</v>
+      </c>
+      <c r="Q15">
+        <v>-17.00087908</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.0809086247689495</v>
+      </c>
+      <c r="T15">
+        <v>0.9154048862815107</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.034866</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>27.67133403299392</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07480077473304229</v>
+      </c>
+      <c r="C16">
+        <v>372.1996246896499</v>
+      </c>
+      <c r="D16">
+        <v>419.7396246896498</v>
+      </c>
+      <c r="E16">
+        <v>59.64000000000001</v>
+      </c>
+      <c r="F16">
+        <v>59.64000000000001</v>
+      </c>
+      <c r="G16">
+        <v>12.1</v>
+      </c>
+      <c r="H16">
+        <v>426</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>-68.5</v>
+      </c>
+      <c r="L16">
+        <v>68.5</v>
+      </c>
+      <c r="M16">
+        <v>2.665908</v>
+      </c>
+      <c r="N16">
+        <v>65.834092</v>
+      </c>
+      <c r="O16">
+        <v>14.48350024</v>
+      </c>
+      <c r="P16">
+        <v>51.35059176</v>
+      </c>
+      <c r="Q16">
+        <v>-17.14940824</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.081301784573305</v>
+      </c>
+      <c r="T16">
+        <v>0.9239518385501087</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.034866</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>25.69481017349435</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.07467846591709854</v>
+      </c>
+      <c r="C17">
+        <v>368.3630524559842</v>
+      </c>
+      <c r="D17">
+        <v>420.1630524559841</v>
+      </c>
+      <c r="E17">
+        <v>63.9</v>
+      </c>
+      <c r="F17">
+        <v>63.9</v>
+      </c>
+      <c r="G17">
+        <v>12.1</v>
+      </c>
+      <c r="H17">
+        <v>426</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-68.5</v>
+      </c>
+      <c r="L17">
+        <v>68.5</v>
+      </c>
+      <c r="M17">
+        <v>2.85633</v>
+      </c>
+      <c r="N17">
+        <v>65.64367</v>
+      </c>
+      <c r="O17">
+        <v>14.4416074</v>
+      </c>
+      <c r="P17">
+        <v>51.2020626</v>
+      </c>
+      <c r="Q17">
+        <v>-17.2979374</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08170419519658652</v>
+      </c>
+      <c r="T17">
+        <v>0.9326998955779677</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.034866</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>23.98182282859473</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07455615710115476</v>
+      </c>
+      <c r="C18">
+        <v>364.5273353816212</v>
+      </c>
+      <c r="D18">
+        <v>420.5873353816212</v>
+      </c>
+      <c r="E18">
+        <v>68.16</v>
+      </c>
+      <c r="F18">
+        <v>68.16</v>
+      </c>
+      <c r="G18">
+        <v>12.1</v>
+      </c>
+      <c r="H18">
+        <v>426</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-68.5</v>
+      </c>
+      <c r="L18">
+        <v>68.5</v>
+      </c>
+      <c r="M18">
+        <v>3.046752</v>
+      </c>
+      <c r="N18">
+        <v>65.453248</v>
+      </c>
+      <c r="O18">
+        <v>14.39971456</v>
+      </c>
+      <c r="P18">
+        <v>51.05353344</v>
+      </c>
+      <c r="Q18">
+        <v>-17.44646656</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08211618702518425</v>
+      </c>
+      <c r="T18">
+        <v>0.9416562396779187</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.034866</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>22.48295890180756</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.074433848285211</v>
+      </c>
+      <c r="C19">
+        <v>360.6924760598133</v>
+      </c>
+      <c r="D19">
+        <v>421.0124760598133</v>
+      </c>
+      <c r="E19">
+        <v>72.42</v>
+      </c>
+      <c r="F19">
+        <v>72.42</v>
+      </c>
+      <c r="G19">
+        <v>12.1</v>
+      </c>
+      <c r="H19">
+        <v>426</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-68.5</v>
+      </c>
+      <c r="L19">
+        <v>68.5</v>
+      </c>
+      <c r="M19">
+        <v>3.237174</v>
+      </c>
+      <c r="N19">
+        <v>65.262826</v>
+      </c>
+      <c r="O19">
+        <v>14.35782172</v>
+      </c>
+      <c r="P19">
+        <v>50.90500428</v>
+      </c>
+      <c r="Q19">
+        <v>-17.59499572</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08253810636772412</v>
+      </c>
+      <c r="T19">
+        <v>0.9508283992983504</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.034866</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>21.16043190758359</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07431153946926726</v>
+      </c>
+      <c r="C20">
+        <v>356.8584770943082</v>
+      </c>
+      <c r="D20">
+        <v>421.4384770943082</v>
+      </c>
+      <c r="E20">
+        <v>76.67999999999999</v>
+      </c>
+      <c r="F20">
+        <v>76.67999999999999</v>
+      </c>
+      <c r="G20">
+        <v>12.1</v>
+      </c>
+      <c r="H20">
+        <v>426</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>-68.5</v>
+      </c>
+      <c r="L20">
+        <v>68.5</v>
+      </c>
+      <c r="M20">
+        <v>3.427596</v>
+      </c>
+      <c r="N20">
+        <v>65.07240400000001</v>
+      </c>
+      <c r="O20">
+        <v>14.31592888</v>
+      </c>
+      <c r="P20">
+        <v>50.75647512</v>
+      </c>
+      <c r="Q20">
+        <v>-17.74352488</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08297031642593568</v>
+      </c>
+      <c r="T20">
+        <v>0.9602242701290364</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.034866</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>19.98485235716228</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.07418923065332349</v>
+      </c>
+      <c r="C21">
+        <v>353.0253410994035</v>
+      </c>
+      <c r="D21">
+        <v>421.8653410994035</v>
+      </c>
+      <c r="E21">
+        <v>80.94</v>
+      </c>
+      <c r="F21">
+        <v>80.94</v>
+      </c>
+      <c r="G21">
+        <v>12.1</v>
+      </c>
+      <c r="H21">
+        <v>426</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-68.5</v>
+      </c>
+      <c r="L21">
+        <v>68.5</v>
+      </c>
+      <c r="M21">
+        <v>3.618018</v>
+      </c>
+      <c r="N21">
+        <v>64.88198199999999</v>
+      </c>
+      <c r="O21">
+        <v>14.27403604</v>
+      </c>
+      <c r="P21">
+        <v>50.60794596</v>
+      </c>
+      <c r="Q21">
+        <v>-17.89205404</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08341319833743641</v>
+      </c>
+      <c r="T21">
+        <v>0.9698521377703568</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.034866</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>18.93301802257479</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.07406692183737974</v>
+      </c>
+      <c r="C22">
+        <v>349.1930706999986</v>
+      </c>
+      <c r="D22">
+        <v>422.2930706999986</v>
+      </c>
+      <c r="E22">
+        <v>85.2</v>
+      </c>
+      <c r="F22">
+        <v>85.2</v>
+      </c>
+      <c r="G22">
+        <v>12.1</v>
+      </c>
+      <c r="H22">
+        <v>426</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-68.5</v>
+      </c>
+      <c r="L22">
+        <v>68.5</v>
+      </c>
+      <c r="M22">
+        <v>3.80844</v>
+      </c>
+      <c r="N22">
+        <v>64.69156</v>
+      </c>
+      <c r="O22">
+        <v>14.2321432</v>
+      </c>
+      <c r="P22">
+        <v>50.4594168</v>
+      </c>
+      <c r="Q22">
+        <v>-18.0405832</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08386715229672467</v>
+      </c>
+      <c r="T22">
+        <v>0.9797207021027102</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.034866</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>17.98636712144605</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.07394461302143597</v>
+      </c>
+      <c r="C23">
+        <v>345.3616685316496</v>
+      </c>
+      <c r="D23">
+        <v>422.7216685316496</v>
+      </c>
+      <c r="E23">
+        <v>89.45999999999999</v>
+      </c>
+      <c r="F23">
+        <v>89.45999999999999</v>
+      </c>
+      <c r="G23">
+        <v>12.1</v>
+      </c>
+      <c r="H23">
+        <v>426</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>-68.5</v>
+      </c>
+      <c r="L23">
+        <v>68.5</v>
+      </c>
+      <c r="M23">
+        <v>3.998862</v>
+      </c>
+      <c r="N23">
+        <v>64.501138</v>
+      </c>
+      <c r="O23">
+        <v>14.19025036</v>
+      </c>
+      <c r="P23">
+        <v>50.31088764</v>
+      </c>
+      <c r="Q23">
+        <v>-18.18911236</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08433259876131136</v>
+      </c>
+      <c r="T23">
+        <v>0.9898391035067685</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.034866</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>17.12987344899624</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07382230420549221</v>
+      </c>
+      <c r="C24">
+        <v>341.5311372406233</v>
+      </c>
+      <c r="D24">
+        <v>423.1511372406232</v>
+      </c>
+      <c r="E24">
+        <v>93.72</v>
+      </c>
+      <c r="F24">
+        <v>93.72</v>
+      </c>
+      <c r="G24">
+        <v>12.1</v>
+      </c>
+      <c r="H24">
+        <v>426</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-68.5</v>
+      </c>
+      <c r="L24">
+        <v>68.5</v>
+      </c>
+      <c r="M24">
+        <v>4.189284000000001</v>
+      </c>
+      <c r="N24">
+        <v>64.310716</v>
+      </c>
+      <c r="O24">
+        <v>14.14835752</v>
+      </c>
+      <c r="P24">
+        <v>50.16235848</v>
+      </c>
+      <c r="Q24">
+        <v>-18.33764152</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08480997975063104</v>
+      </c>
+      <c r="T24">
+        <v>1.000216951100675</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.034866</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>16.35124283767823</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.07369999538954845</v>
+      </c>
+      <c r="C25">
+        <v>337.7014794839508</v>
+      </c>
+      <c r="D25">
+        <v>423.5814794839508</v>
+      </c>
+      <c r="E25">
+        <v>97.98</v>
+      </c>
+      <c r="F25">
+        <v>97.98</v>
+      </c>
+      <c r="G25">
+        <v>12.1</v>
+      </c>
+      <c r="H25">
+        <v>426</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-68.5</v>
+      </c>
+      <c r="L25">
+        <v>68.5</v>
+      </c>
+      <c r="M25">
+        <v>4.379706000000001</v>
+      </c>
+      <c r="N25">
+        <v>64.120294</v>
+      </c>
+      <c r="O25">
+        <v>14.10646468</v>
+      </c>
+      <c r="P25">
+        <v>50.01382932</v>
+      </c>
+      <c r="Q25">
+        <v>-18.48617068</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08529976024616683</v>
+      </c>
+      <c r="T25">
+        <v>1.01086435317754</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.034866</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>15.64031923604004</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.07357768657360469</v>
+      </c>
+      <c r="C26">
+        <v>333.8726979294836</v>
+      </c>
+      <c r="D26">
+        <v>424.0126979294836</v>
+      </c>
+      <c r="E26">
+        <v>102.24</v>
+      </c>
+      <c r="F26">
+        <v>102.24</v>
+      </c>
+      <c r="G26">
+        <v>12.1</v>
+      </c>
+      <c r="H26">
+        <v>426</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>-68.5</v>
+      </c>
+      <c r="L26">
+        <v>68.5</v>
+      </c>
+      <c r="M26">
+        <v>4.570128</v>
+      </c>
+      <c r="N26">
+        <v>63.929872</v>
+      </c>
+      <c r="O26">
+        <v>14.06457184</v>
+      </c>
+      <c r="P26">
+        <v>49.86530016</v>
+      </c>
+      <c r="Q26">
+        <v>-18.63469984</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08580242970211144</v>
+      </c>
+      <c r="T26">
+        <v>1.021791950045901</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.034866</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>14.98863926787171</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.07345537775766094</v>
+      </c>
+      <c r="C27">
+        <v>330.0447952559479</v>
+      </c>
+      <c r="D27">
+        <v>424.4447952559478</v>
+      </c>
+      <c r="E27">
+        <v>106.5</v>
+      </c>
+      <c r="F27">
+        <v>106.5</v>
+      </c>
+      <c r="G27">
+        <v>12.1</v>
+      </c>
+      <c r="H27">
+        <v>426</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-68.5</v>
+      </c>
+      <c r="L27">
+        <v>68.5</v>
+      </c>
+      <c r="M27">
+        <v>4.76055</v>
+      </c>
+      <c r="N27">
+        <v>63.73945</v>
+      </c>
+      <c r="O27">
+        <v>14.022679</v>
+      </c>
+      <c r="P27">
+        <v>49.71677099999999</v>
+      </c>
+      <c r="Q27">
+        <v>-18.78322900000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08631850367688124</v>
+      </c>
+      <c r="T27">
+        <v>1.033010949497418</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.034866</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>14.38909369715684</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.07333306894171718</v>
+      </c>
+      <c r="C28">
+        <v>326.2177741529999</v>
+      </c>
+      <c r="D28">
+        <v>424.8777741529998</v>
+      </c>
+      <c r="E28">
+        <v>110.76</v>
+      </c>
+      <c r="F28">
+        <v>110.76</v>
+      </c>
+      <c r="G28">
+        <v>12.1</v>
+      </c>
+      <c r="H28">
+        <v>426</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-68.5</v>
+      </c>
+      <c r="L28">
+        <v>68.5</v>
+      </c>
+      <c r="M28">
+        <v>4.950972000000001</v>
+      </c>
+      <c r="N28">
+        <v>63.549028</v>
+      </c>
+      <c r="O28">
+        <v>13.98078616</v>
+      </c>
+      <c r="P28">
+        <v>49.56824184</v>
+      </c>
+      <c r="Q28">
+        <v>-18.93175816</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.0868485255969151</v>
+      </c>
+      <c r="T28">
+        <v>1.044533165150328</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.034866</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>13.83566701649696</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.07321076012577341</v>
+      </c>
+      <c r="C29">
+        <v>322.3916373212825</v>
+      </c>
+      <c r="D29">
+        <v>425.3116373212824</v>
+      </c>
+      <c r="E29">
+        <v>115.02</v>
+      </c>
+      <c r="F29">
+        <v>115.02</v>
+      </c>
+      <c r="G29">
+        <v>12.1</v>
+      </c>
+      <c r="H29">
+        <v>426</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-68.5</v>
+      </c>
+      <c r="L29">
+        <v>68.5</v>
+      </c>
+      <c r="M29">
+        <v>5.141394000000001</v>
+      </c>
+      <c r="N29">
+        <v>63.358606</v>
+      </c>
+      <c r="O29">
+        <v>13.93889332</v>
+      </c>
+      <c r="P29">
+        <v>49.41971268</v>
+      </c>
+      <c r="Q29">
+        <v>-19.08028732</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.08739306866544302</v>
+      </c>
+      <c r="T29">
+        <v>1.056371057944414</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.034866</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>13.32323490477485</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.07308845130982966</v>
+      </c>
+      <c r="C30">
+        <v>318.5663874724803</v>
+      </c>
+      <c r="D30">
+        <v>425.7463874724803</v>
+      </c>
+      <c r="E30">
+        <v>119.28</v>
+      </c>
+      <c r="F30">
+        <v>119.28</v>
+      </c>
+      <c r="G30">
+        <v>12.1</v>
+      </c>
+      <c r="H30">
+        <v>426</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>-68.5</v>
+      </c>
+      <c r="L30">
+        <v>68.5</v>
+      </c>
+      <c r="M30">
+        <v>5.331816000000001</v>
+      </c>
+      <c r="N30">
+        <v>63.168184</v>
+      </c>
+      <c r="O30">
+        <v>13.89700048</v>
+      </c>
+      <c r="P30">
+        <v>49.27118351999999</v>
+      </c>
+      <c r="Q30">
+        <v>-19.22881648000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.08795273793031896</v>
+      </c>
+      <c r="T30">
+        <v>1.06853778109389</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.034866</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>12.84740508674718</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.07321496249388589</v>
+      </c>
+      <c r="C31">
+        <v>313.8567156616434</v>
+      </c>
+      <c r="D31">
+        <v>425.2967156616434</v>
+      </c>
+      <c r="E31">
+        <v>123.54</v>
+      </c>
+      <c r="F31">
+        <v>123.54</v>
+      </c>
+      <c r="G31">
+        <v>12.1</v>
+      </c>
+      <c r="H31">
+        <v>426</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>-68.5</v>
+      </c>
+      <c r="L31">
+        <v>68.5</v>
+      </c>
+      <c r="M31">
+        <v>5.658131999999999</v>
+      </c>
+      <c r="N31">
+        <v>62.841868</v>
+      </c>
+      <c r="O31">
+        <v>13.82521096</v>
+      </c>
+      <c r="P31">
+        <v>49.01665704</v>
+      </c>
+      <c r="Q31">
+        <v>-19.48334296</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.08852817252659984</v>
+      </c>
+      <c r="T31">
+        <v>1.081047228839127</v>
+      </c>
+      <c r="U31">
+        <v>0.0458</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.035724</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>12.10646906081371</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.07310123367794212</v>
+      </c>
+      <c r="C32">
+        <v>310.0009105975336</v>
+      </c>
+      <c r="D32">
+        <v>425.7009105975336</v>
+      </c>
+      <c r="E32">
+        <v>127.8</v>
+      </c>
+      <c r="F32">
+        <v>127.8</v>
+      </c>
+      <c r="G32">
+        <v>12.1</v>
+      </c>
+      <c r="H32">
+        <v>426</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>-68.5</v>
+      </c>
+      <c r="L32">
+        <v>68.5</v>
+      </c>
+      <c r="M32">
+        <v>5.85324</v>
+      </c>
+      <c r="N32">
+        <v>62.64676</v>
+      </c>
+      <c r="O32">
+        <v>13.7822872</v>
+      </c>
+      <c r="P32">
+        <v>48.8644728</v>
+      </c>
+      <c r="Q32">
+        <v>-19.6355272</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.0891200481113459</v>
+      </c>
+      <c r="T32">
+        <v>1.093914089377085</v>
+      </c>
+      <c r="U32">
+        <v>0.0458</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.035724</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>11.70292009211992</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.07298750486199836</v>
+      </c>
+      <c r="C33">
+        <v>306.1458745445888</v>
+      </c>
+      <c r="D33">
+        <v>426.1058745445887</v>
+      </c>
+      <c r="E33">
+        <v>132.06</v>
+      </c>
+      <c r="F33">
+        <v>132.06</v>
+      </c>
+      <c r="G33">
+        <v>12.1</v>
+      </c>
+      <c r="H33">
+        <v>426</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>-68.5</v>
+      </c>
+      <c r="L33">
+        <v>68.5</v>
+      </c>
+      <c r="M33">
+        <v>6.048348</v>
+      </c>
+      <c r="N33">
+        <v>62.451652</v>
+      </c>
+      <c r="O33">
+        <v>13.73936344</v>
+      </c>
+      <c r="P33">
+        <v>48.71228856</v>
+      </c>
+      <c r="Q33">
+        <v>-19.78771144</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.08972907951014256</v>
+      </c>
+      <c r="T33">
+        <v>1.107153902394403</v>
+      </c>
+      <c r="U33">
+        <v>0.0458</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.035724</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>11.32540654076121</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.07287377604605461</v>
+      </c>
+      <c r="C34">
+        <v>302.2916096995509</v>
+      </c>
+      <c r="D34">
+        <v>426.5116096995508</v>
+      </c>
+      <c r="E34">
+        <v>136.32</v>
+      </c>
+      <c r="F34">
+        <v>136.32</v>
+      </c>
+      <c r="G34">
+        <v>12.1</v>
+      </c>
+      <c r="H34">
+        <v>426</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>-68.5</v>
+      </c>
+      <c r="L34">
+        <v>68.5</v>
+      </c>
+      <c r="M34">
+        <v>6.243456</v>
+      </c>
+      <c r="N34">
+        <v>62.256544</v>
+      </c>
+      <c r="O34">
+        <v>13.69643968</v>
+      </c>
+      <c r="P34">
+        <v>48.56010432</v>
+      </c>
+      <c r="Q34">
+        <v>-19.93989568</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09035602359713912</v>
+      </c>
+      <c r="T34">
+        <v>1.120783121676937</v>
+      </c>
+      <c r="U34">
+        <v>0.0458</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.035724</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>10.97148758636243</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.07276004723011084</v>
+      </c>
+      <c r="C35">
+        <v>298.4381182675365</v>
+      </c>
+      <c r="D35">
+        <v>426.9181182675365</v>
+      </c>
+      <c r="E35">
+        <v>140.58</v>
+      </c>
+      <c r="F35">
+        <v>140.58</v>
+      </c>
+      <c r="G35">
+        <v>12.1</v>
+      </c>
+      <c r="H35">
+        <v>426</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-68.5</v>
+      </c>
+      <c r="L35">
+        <v>68.5</v>
+      </c>
+      <c r="M35">
+        <v>6.438564</v>
+      </c>
+      <c r="N35">
+        <v>62.061436</v>
+      </c>
+      <c r="O35">
+        <v>13.65351592</v>
+      </c>
+      <c r="P35">
+        <v>48.40792008</v>
+      </c>
+      <c r="Q35">
+        <v>-20.09207992</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09100168243300126</v>
+      </c>
+      <c r="T35">
+        <v>1.134819183326114</v>
+      </c>
+      <c r="U35">
+        <v>0.0458</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.035724</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>10.63901826556356</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.07264631841416706</v>
+      </c>
+      <c r="C36">
+        <v>294.5854024620774</v>
+      </c>
+      <c r="D36">
+        <v>427.3254024620773</v>
+      </c>
+      <c r="E36">
+        <v>144.84</v>
+      </c>
+      <c r="F36">
+        <v>144.84</v>
+      </c>
+      <c r="G36">
+        <v>12.1</v>
+      </c>
+      <c r="H36">
+        <v>426</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>-68.5</v>
+      </c>
+      <c r="L36">
+        <v>68.5</v>
+      </c>
+      <c r="M36">
+        <v>6.633672</v>
+      </c>
+      <c r="N36">
+        <v>61.866328</v>
+      </c>
+      <c r="O36">
+        <v>13.61059216</v>
+      </c>
+      <c r="P36">
+        <v>48.25573584</v>
+      </c>
+      <c r="Q36">
+        <v>-20.24426416</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09166690668813193</v>
+      </c>
+      <c r="T36">
+        <v>1.149280580176781</v>
+      </c>
+      <c r="U36">
+        <v>0.0458</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.035724</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>10.32610596363523</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.07253258959822331</v>
+      </c>
+      <c r="C37">
+        <v>290.7334645051596</v>
+      </c>
+      <c r="D37">
+        <v>427.7334645051596</v>
+      </c>
+      <c r="E37">
+        <v>149.1</v>
+      </c>
+      <c r="F37">
+        <v>149.1</v>
+      </c>
+      <c r="G37">
+        <v>12.1</v>
+      </c>
+      <c r="H37">
+        <v>426</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>-68.5</v>
+      </c>
+      <c r="L37">
+        <v>68.5</v>
+      </c>
+      <c r="M37">
+        <v>6.828780000000001</v>
+      </c>
+      <c r="N37">
+        <v>61.67122</v>
+      </c>
+      <c r="O37">
+        <v>13.5676684</v>
+      </c>
+      <c r="P37">
+        <v>48.1035516</v>
+      </c>
+      <c r="Q37">
+        <v>-20.3964484</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09235259938188203</v>
+      </c>
+      <c r="T37">
+        <v>1.164186943084392</v>
+      </c>
+      <c r="U37">
+        <v>0.0458</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.035724</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>10.03107436467421</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.07303662078227956</v>
+      </c>
+      <c r="C38">
+        <v>284.670888793359</v>
+      </c>
+      <c r="D38">
+        <v>425.930888793359</v>
+      </c>
+      <c r="E38">
+        <v>153.36</v>
+      </c>
+      <c r="F38">
+        <v>153.36</v>
+      </c>
+      <c r="G38">
+        <v>12.1</v>
+      </c>
+      <c r="H38">
+        <v>426</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-68.5</v>
+      </c>
+      <c r="L38">
+        <v>68.5</v>
+      </c>
+      <c r="M38">
+        <v>7.36128</v>
+      </c>
+      <c r="N38">
+        <v>61.13872</v>
+      </c>
+      <c r="O38">
+        <v>13.4505184</v>
+      </c>
+      <c r="P38">
+        <v>47.6882016</v>
+      </c>
+      <c r="Q38">
+        <v>-20.8117984</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.0930597199723118</v>
+      </c>
+      <c r="T38">
+        <v>1.179559129832865</v>
+      </c>
+      <c r="U38">
+        <v>0.048</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.03744</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>9.305446878803686</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.07294005196633579</v>
+      </c>
+      <c r="C39">
+        <v>280.7550720358925</v>
+      </c>
+      <c r="D39">
+        <v>426.2750720358924</v>
+      </c>
+      <c r="E39">
+        <v>157.62</v>
+      </c>
+      <c r="F39">
+        <v>157.62</v>
+      </c>
+      <c r="G39">
+        <v>12.1</v>
+      </c>
+      <c r="H39">
+        <v>426</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>-68.5</v>
+      </c>
+      <c r="L39">
+        <v>68.5</v>
+      </c>
+      <c r="M39">
+        <v>7.56576</v>
+      </c>
+      <c r="N39">
+        <v>60.93424</v>
+      </c>
+      <c r="O39">
+        <v>13.4055328</v>
+      </c>
+      <c r="P39">
+        <v>47.5287072</v>
+      </c>
+      <c r="Q39">
+        <v>-20.9712928</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09378928883545365</v>
+      </c>
+      <c r="T39">
+        <v>1.195419322509862</v>
+      </c>
+      <c r="U39">
+        <v>0.048</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.03744</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>9.053948314511695</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.07284348315039203</v>
+      </c>
+      <c r="C40">
+        <v>276.8398119786372</v>
+      </c>
+      <c r="D40">
+        <v>426.6198119786371</v>
+      </c>
+      <c r="E40">
+        <v>161.88</v>
+      </c>
+      <c r="F40">
+        <v>161.88</v>
+      </c>
+      <c r="G40">
+        <v>12.1</v>
+      </c>
+      <c r="H40">
+        <v>426</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>-68.5</v>
+      </c>
+      <c r="L40">
+        <v>68.5</v>
+      </c>
+      <c r="M40">
+        <v>7.77024</v>
+      </c>
+      <c r="N40">
+        <v>60.72976</v>
+      </c>
+      <c r="O40">
+        <v>13.3605472</v>
+      </c>
+      <c r="P40">
+        <v>47.3692128</v>
+      </c>
+      <c r="Q40">
+        <v>-21.1307872</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.09454239217805166</v>
+      </c>
+      <c r="T40">
+        <v>1.211791134305471</v>
+      </c>
+      <c r="U40">
+        <v>0.048</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.03744</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>8.815686516761387</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.07274691433444827</v>
+      </c>
+      <c r="C41">
+        <v>272.9251099733408</v>
+      </c>
+      <c r="D41">
+        <v>426.9651099733408</v>
+      </c>
+      <c r="E41">
+        <v>166.14</v>
+      </c>
+      <c r="F41">
+        <v>166.14</v>
+      </c>
+      <c r="G41">
+        <v>12.1</v>
+      </c>
+      <c r="H41">
+        <v>426</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>-68.5</v>
+      </c>
+      <c r="L41">
+        <v>68.5</v>
+      </c>
+      <c r="M41">
+        <v>7.97472</v>
+      </c>
+      <c r="N41">
+        <v>60.52528</v>
+      </c>
+      <c r="O41">
+        <v>13.3155616</v>
+      </c>
+      <c r="P41">
+        <v>47.2097184</v>
+      </c>
+      <c r="Q41">
+        <v>-21.2902816</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.09532018743352176</v>
+      </c>
+      <c r="T41">
+        <v>1.228699726815691</v>
+      </c>
+      <c r="U41">
+        <v>0.048</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.03744</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>8.589643272741863</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.07265034551850452</v>
+      </c>
+      <c r="C42">
+        <v>269.0109673761312</v>
+      </c>
+      <c r="D42">
+        <v>427.3109673761313</v>
+      </c>
+      <c r="E42">
+        <v>170.4</v>
+      </c>
+      <c r="F42">
+        <v>170.4</v>
+      </c>
+      <c r="G42">
+        <v>12.1</v>
+      </c>
+      <c r="H42">
+        <v>426</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>-68.5</v>
+      </c>
+      <c r="L42">
+        <v>68.5</v>
+      </c>
+      <c r="M42">
+        <v>8.1792</v>
+      </c>
+      <c r="N42">
+        <v>60.3208</v>
+      </c>
+      <c r="O42">
+        <v>13.270576</v>
+      </c>
+      <c r="P42">
+        <v>47.050224</v>
+      </c>
+      <c r="Q42">
+        <v>-21.449776</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.09612390919750753</v>
+      </c>
+      <c r="T42">
+        <v>1.246171939076251</v>
+      </c>
+      <c r="U42">
+        <v>0.048</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.03744</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>8.374902190923319</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.07255377670256076</v>
+      </c>
+      <c r="C43">
+        <v>265.0973855475337</v>
+      </c>
+      <c r="D43">
+        <v>427.6573855475337</v>
+      </c>
+      <c r="E43">
+        <v>174.66</v>
+      </c>
+      <c r="F43">
+        <v>174.66</v>
+      </c>
+      <c r="G43">
+        <v>12.1</v>
+      </c>
+      <c r="H43">
+        <v>426</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>-68.5</v>
+      </c>
+      <c r="L43">
+        <v>68.5</v>
+      </c>
+      <c r="M43">
+        <v>8.383680000000002</v>
+      </c>
+      <c r="N43">
+        <v>60.11632</v>
+      </c>
+      <c r="O43">
+        <v>13.2255904</v>
+      </c>
+      <c r="P43">
+        <v>46.8907296</v>
+      </c>
+      <c r="Q43">
+        <v>-21.6092704</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.09695487576705213</v>
+      </c>
+      <c r="T43">
+        <v>1.264236429718524</v>
+      </c>
+      <c r="U43">
+        <v>0.048</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.03744</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>8.170636283827626</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.072457207886617</v>
+      </c>
+      <c r="C44">
+        <v>261.184365852489</v>
+      </c>
+      <c r="D44">
+        <v>428.0043658524889</v>
+      </c>
+      <c r="E44">
+        <v>178.92</v>
+      </c>
+      <c r="F44">
+        <v>178.92</v>
+      </c>
+      <c r="G44">
+        <v>12.1</v>
+      </c>
+      <c r="H44">
+        <v>426</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>-68.5</v>
+      </c>
+      <c r="L44">
+        <v>68.5</v>
+      </c>
+      <c r="M44">
+        <v>8.58816</v>
+      </c>
+      <c r="N44">
+        <v>59.91184</v>
+      </c>
+      <c r="O44">
+        <v>13.1806048</v>
+      </c>
+      <c r="P44">
+        <v>46.7312352</v>
+      </c>
+      <c r="Q44">
+        <v>-21.7687648</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.09781449635623619</v>
+      </c>
+      <c r="T44">
+        <v>1.282923833831222</v>
+      </c>
+      <c r="U44">
+        <v>0.048</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.03744</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>7.976097324688873</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.07236063907067324</v>
+      </c>
+      <c r="C45">
+        <v>257.2719096603712</v>
+      </c>
+      <c r="D45">
+        <v>428.3519096603712</v>
+      </c>
+      <c r="E45">
+        <v>183.18</v>
+      </c>
+      <c r="F45">
+        <v>183.18</v>
+      </c>
+      <c r="G45">
+        <v>12.1</v>
+      </c>
+      <c r="H45">
+        <v>426</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>-68.5</v>
+      </c>
+      <c r="L45">
+        <v>68.5</v>
+      </c>
+      <c r="M45">
+        <v>8.79264</v>
+      </c>
+      <c r="N45">
+        <v>59.70736</v>
+      </c>
+      <c r="O45">
+        <v>13.1356192</v>
+      </c>
+      <c r="P45">
+        <v>46.5717408</v>
+      </c>
+      <c r="Q45">
+        <v>-21.9282592</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.09870427907135654</v>
+      </c>
+      <c r="T45">
+        <v>1.302266936333838</v>
+      </c>
+      <c r="U45">
+        <v>0.048</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.03744</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>7.790606689230993</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.07277887025472948</v>
+      </c>
+      <c r="C46">
+        <v>251.5107843592895</v>
+      </c>
+      <c r="D46">
+        <v>426.8507843592895</v>
+      </c>
+      <c r="E46">
+        <v>187.44</v>
+      </c>
+      <c r="F46">
+        <v>187.44</v>
+      </c>
+      <c r="G46">
+        <v>12.1</v>
+      </c>
+      <c r="H46">
+        <v>426</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>-68.5</v>
+      </c>
+      <c r="L46">
+        <v>68.5</v>
+      </c>
+      <c r="M46">
+        <v>9.278280000000001</v>
+      </c>
+      <c r="N46">
+        <v>59.22172</v>
+      </c>
+      <c r="O46">
+        <v>13.0287784</v>
+      </c>
+      <c r="P46">
+        <v>46.1929416</v>
+      </c>
+      <c r="Q46">
+        <v>-22.3070584</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.09962583974058833</v>
+      </c>
+      <c r="T46">
+        <v>1.322300863925834</v>
+      </c>
+      <c r="U46">
+        <v>0.0495</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>7.382833887315321</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.07269400143878571</v>
+      </c>
+      <c r="C47">
+        <v>247.554546050409</v>
+      </c>
+      <c r="D47">
+        <v>427.154546050409</v>
+      </c>
+      <c r="E47">
+        <v>191.7</v>
+      </c>
+      <c r="F47">
+        <v>191.7</v>
+      </c>
+      <c r="G47">
+        <v>12.1</v>
+      </c>
+      <c r="H47">
+        <v>426</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>-68.5</v>
+      </c>
+      <c r="L47">
+        <v>68.5</v>
+      </c>
+      <c r="M47">
+        <v>9.48915</v>
+      </c>
+      <c r="N47">
+        <v>59.01085</v>
+      </c>
+      <c r="O47">
+        <v>12.982387</v>
+      </c>
+      <c r="P47">
+        <v>46.028463</v>
+      </c>
+      <c r="Q47">
+        <v>-22.471537</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1005809117068831</v>
+      </c>
+      <c r="T47">
+        <v>1.34306329797572</v>
+      </c>
+      <c r="U47">
+        <v>0.0495</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>7.218770912041647</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.07260913262284195</v>
+      </c>
+      <c r="C48">
+        <v>243.5987403839339</v>
+      </c>
+      <c r="D48">
+        <v>427.4587403839338</v>
+      </c>
+      <c r="E48">
+        <v>195.96</v>
+      </c>
+      <c r="F48">
+        <v>195.96</v>
+      </c>
+      <c r="G48">
+        <v>12.1</v>
+      </c>
+      <c r="H48">
+        <v>426</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>-68.5</v>
+      </c>
+      <c r="L48">
+        <v>68.5</v>
+      </c>
+      <c r="M48">
+        <v>9.70002</v>
+      </c>
+      <c r="N48">
+        <v>58.79998</v>
+      </c>
+      <c r="O48">
+        <v>12.9359956</v>
+      </c>
+      <c r="P48">
+        <v>45.8639844</v>
+      </c>
+      <c r="Q48">
+        <v>-22.6360156</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1015713567089666</v>
+      </c>
+      <c r="T48">
+        <v>1.364594711064491</v>
+      </c>
+      <c r="U48">
+        <v>0.0495</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>7.061841109605959</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.07252426380689819</v>
+      </c>
+      <c r="C49">
+        <v>239.6433682848305</v>
+      </c>
+      <c r="D49">
+        <v>427.7633682848304</v>
+      </c>
+      <c r="E49">
+        <v>200.22</v>
+      </c>
+      <c r="F49">
+        <v>200.22</v>
+      </c>
+      <c r="G49">
+        <v>12.1</v>
+      </c>
+      <c r="H49">
+        <v>426</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>-68.5</v>
+      </c>
+      <c r="L49">
+        <v>68.5</v>
+      </c>
+      <c r="M49">
+        <v>9.91089</v>
+      </c>
+      <c r="N49">
+        <v>58.58911</v>
+      </c>
+      <c r="O49">
+        <v>12.8896042</v>
+      </c>
+      <c r="P49">
+        <v>45.6995058</v>
+      </c>
+      <c r="Q49">
+        <v>-22.8004942</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1025991769941475</v>
+      </c>
+      <c r="T49">
+        <v>1.386938630307555</v>
+      </c>
+      <c r="U49">
+        <v>0.0495</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>6.911589171103705</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.07243939499095443</v>
+      </c>
+      <c r="C50">
+        <v>235.6884306807035</v>
+      </c>
+      <c r="D50">
+        <v>428.0684306807034</v>
+      </c>
+      <c r="E50">
+        <v>204.48</v>
+      </c>
+      <c r="F50">
+        <v>204.48</v>
+      </c>
+      <c r="G50">
+        <v>12.1</v>
+      </c>
+      <c r="H50">
+        <v>426</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>-68.5</v>
+      </c>
+      <c r="L50">
+        <v>68.5</v>
+      </c>
+      <c r="M50">
+        <v>10.12176</v>
+      </c>
+      <c r="N50">
+        <v>58.37824</v>
+      </c>
+      <c r="O50">
+        <v>12.8432128</v>
+      </c>
+      <c r="P50">
+        <v>45.5350272</v>
+      </c>
+      <c r="Q50">
+        <v>-22.9649728</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1036665288287585</v>
+      </c>
+      <c r="T50">
+        <v>1.410141931059968</v>
+      </c>
+      <c r="U50">
+        <v>0.0495</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>6.767597730039045</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.07235452617501067</v>
+      </c>
+      <c r="C51">
+        <v>231.7339285018055</v>
+      </c>
+      <c r="D51">
+        <v>428.3739285018054</v>
+      </c>
+      <c r="E51">
+        <v>208.74</v>
+      </c>
+      <c r="F51">
+        <v>208.74</v>
+      </c>
+      <c r="G51">
+        <v>12.1</v>
+      </c>
+      <c r="H51">
+        <v>426</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>-68.5</v>
+      </c>
+      <c r="L51">
+        <v>68.5</v>
+      </c>
+      <c r="M51">
+        <v>10.33263</v>
+      </c>
+      <c r="N51">
+        <v>58.16737</v>
+      </c>
+      <c r="O51">
+        <v>12.7968214</v>
+      </c>
+      <c r="P51">
+        <v>45.3705486</v>
+      </c>
+      <c r="Q51">
+        <v>-23.1294514</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1047757375980601</v>
+      </c>
+      <c r="T51">
+        <v>1.43425516517522</v>
+      </c>
+      <c r="U51">
+        <v>0.0495</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>6.629483490650491</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.0722696573590669</v>
+      </c>
+      <c r="C52">
+        <v>227.7798626810468</v>
+      </c>
+      <c r="D52">
+        <v>428.6798626810468</v>
+      </c>
+      <c r="E52">
+        <v>213</v>
+      </c>
+      <c r="F52">
+        <v>213</v>
+      </c>
+      <c r="G52">
+        <v>12.1</v>
+      </c>
+      <c r="H52">
+        <v>426</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>-68.5</v>
+      </c>
+      <c r="L52">
+        <v>68.5</v>
+      </c>
+      <c r="M52">
+        <v>10.5435</v>
+      </c>
+      <c r="N52">
+        <v>57.9565</v>
+      </c>
+      <c r="O52">
+        <v>12.75043</v>
+      </c>
+      <c r="P52">
+        <v>45.20607</v>
+      </c>
+      <c r="Q52">
+        <v>-23.29393</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1059293147181338</v>
+      </c>
+      <c r="T52">
+        <v>1.459332928655083</v>
+      </c>
+      <c r="U52">
+        <v>0.0495</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>6.496893820837482</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.07218478854312316</v>
+      </c>
+      <c r="C53">
+        <v>223.8262341540042</v>
+      </c>
+      <c r="D53">
+        <v>428.9862341540041</v>
+      </c>
+      <c r="E53">
+        <v>217.26</v>
+      </c>
+      <c r="F53">
+        <v>217.26</v>
+      </c>
+      <c r="G53">
+        <v>12.1</v>
+      </c>
+      <c r="H53">
+        <v>426</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>-68.5</v>
+      </c>
+      <c r="L53">
+        <v>68.5</v>
+      </c>
+      <c r="M53">
+        <v>10.75437</v>
+      </c>
+      <c r="N53">
+        <v>57.74563</v>
+      </c>
+      <c r="O53">
+        <v>12.7040386</v>
+      </c>
+      <c r="P53">
+        <v>45.0415914</v>
+      </c>
+      <c r="Q53">
+        <v>-23.4584086</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1071299766186187</v>
+      </c>
+      <c r="T53">
+        <v>1.485434274317797</v>
+      </c>
+      <c r="U53">
+        <v>0.0495</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>6.369503745919101</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.07209991972717938</v>
+      </c>
+      <c r="C54">
+        <v>219.8730438589316</v>
+      </c>
+      <c r="D54">
+        <v>429.2930438589316</v>
+      </c>
+      <c r="E54">
+        <v>221.52</v>
+      </c>
+      <c r="F54">
+        <v>221.52</v>
+      </c>
+      <c r="G54">
+        <v>12.1</v>
+      </c>
+      <c r="H54">
+        <v>426</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>-68.5</v>
+      </c>
+      <c r="L54">
+        <v>68.5</v>
+      </c>
+      <c r="M54">
+        <v>10.96524</v>
+      </c>
+      <c r="N54">
+        <v>57.53476</v>
+      </c>
+      <c r="O54">
+        <v>12.6576472</v>
+      </c>
+      <c r="P54">
+        <v>44.8771128</v>
+      </c>
+      <c r="Q54">
+        <v>-23.6228872</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1083806660982904</v>
+      </c>
+      <c r="T54">
+        <v>1.512623176049791</v>
+      </c>
+      <c r="U54">
+        <v>0.0495</v>
+      </c>
+      <c r="V54">
+        <v>0.22</v>
+      </c>
+      <c r="W54">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>6.24701328926681</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.07259381091123562</v>
+      </c>
+      <c r="C55">
+        <v>213.833703996311</v>
+      </c>
+      <c r="D55">
+        <v>427.5137039963109</v>
+      </c>
+      <c r="E55">
+        <v>225.78</v>
+      </c>
+      <c r="F55">
+        <v>225.78</v>
+      </c>
+      <c r="G55">
+        <v>12.1</v>
+      </c>
+      <c r="H55">
+        <v>426</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>-68.5</v>
+      </c>
+      <c r="L55">
+        <v>68.5</v>
+      </c>
+      <c r="M55">
+        <v>11.492202</v>
+      </c>
+      <c r="N55">
+        <v>57.007798</v>
+      </c>
+      <c r="O55">
+        <v>12.54171556</v>
+      </c>
+      <c r="P55">
+        <v>44.46608244</v>
+      </c>
+      <c r="Q55">
+        <v>-24.03391756</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1096845764068843</v>
+      </c>
+      <c r="T55">
+        <v>1.540969052323572</v>
+      </c>
+      <c r="U55">
+        <v>0.0509</v>
+      </c>
+      <c r="V55">
+        <v>0.22</v>
+      </c>
+      <c r="W55">
+        <v>0.039702</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>5.960563519506532</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.07251986209529186</v>
+      </c>
+      <c r="C56">
+        <v>209.8391796205908</v>
+      </c>
+      <c r="D56">
+        <v>427.7791796205908</v>
+      </c>
+      <c r="E56">
+        <v>230.04</v>
+      </c>
+      <c r="F56">
+        <v>230.04</v>
+      </c>
+      <c r="G56">
+        <v>12.1</v>
+      </c>
+      <c r="H56">
+        <v>426</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>-68.5</v>
+      </c>
+      <c r="L56">
+        <v>68.5</v>
+      </c>
+      <c r="M56">
+        <v>11.709036</v>
+      </c>
+      <c r="N56">
+        <v>56.790964</v>
+      </c>
+      <c r="O56">
+        <v>12.49401208</v>
+      </c>
+      <c r="P56">
+        <v>44.29695192</v>
+      </c>
+      <c r="Q56">
+        <v>-24.20304808</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1110451784680258</v>
+      </c>
+      <c r="T56">
+        <v>1.570547358000561</v>
+      </c>
+      <c r="U56">
+        <v>0.0509</v>
+      </c>
+      <c r="V56">
+        <v>0.22</v>
+      </c>
+      <c r="W56">
+        <v>0.039702</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>5.850182713589744</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.0724459132793481</v>
+      </c>
+      <c r="C57">
+        <v>205.844985157565</v>
+      </c>
+      <c r="D57">
+        <v>428.044985157565</v>
+      </c>
+      <c r="E57">
+        <v>234.3</v>
+      </c>
+      <c r="F57">
+        <v>234.3</v>
+      </c>
+      <c r="G57">
+        <v>12.1</v>
+      </c>
+      <c r="H57">
+        <v>426</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>-68.5</v>
+      </c>
+      <c r="L57">
+        <v>68.5</v>
+      </c>
+      <c r="M57">
+        <v>11.92587</v>
+      </c>
+      <c r="N57">
+        <v>56.57413</v>
+      </c>
+      <c r="O57">
+        <v>12.4463086</v>
+      </c>
+      <c r="P57">
+        <v>44.12782139999999</v>
+      </c>
+      <c r="Q57">
+        <v>-24.37217860000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1124662517318847</v>
+      </c>
+      <c r="T57">
+        <v>1.601440255040971</v>
+      </c>
+      <c r="U57">
+        <v>0.0509</v>
+      </c>
+      <c r="V57">
+        <v>0.22</v>
+      </c>
+      <c r="W57">
+        <v>0.039702</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>5.743815755160838</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.07237196446340434</v>
+      </c>
+      <c r="C58">
+        <v>201.851121222601</v>
+      </c>
+      <c r="D58">
+        <v>428.311121222601</v>
+      </c>
+      <c r="E58">
+        <v>238.56</v>
+      </c>
+      <c r="F58">
+        <v>238.56</v>
+      </c>
+      <c r="G58">
+        <v>12.1</v>
+      </c>
+      <c r="H58">
+        <v>426</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>-68.5</v>
+      </c>
+      <c r="L58">
+        <v>68.5</v>
+      </c>
+      <c r="M58">
+        <v>12.142704</v>
+      </c>
+      <c r="N58">
+        <v>56.357296</v>
+      </c>
+      <c r="O58">
+        <v>12.39860512</v>
+      </c>
+      <c r="P58">
+        <v>43.95869088</v>
+      </c>
+      <c r="Q58">
+        <v>-24.54130912</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1139519192350099</v>
+      </c>
+      <c r="T58">
+        <v>1.633737374674128</v>
+      </c>
+      <c r="U58">
+        <v>0.0509</v>
+      </c>
+      <c r="V58">
+        <v>0.22</v>
+      </c>
+      <c r="W58">
+        <v>0.039702</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>5.641247616675823</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.07229801564746058</v>
+      </c>
+      <c r="C59">
+        <v>197.857588432598</v>
+      </c>
+      <c r="D59">
+        <v>428.577588432598</v>
+      </c>
+      <c r="E59">
+        <v>242.82</v>
+      </c>
+      <c r="F59">
+        <v>242.82</v>
+      </c>
+      <c r="G59">
+        <v>12.1</v>
+      </c>
+      <c r="H59">
+        <v>426</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>-68.5</v>
+      </c>
+      <c r="L59">
+        <v>68.5</v>
+      </c>
+      <c r="M59">
+        <v>12.359538</v>
+      </c>
+      <c r="N59">
+        <v>56.140462</v>
+      </c>
+      <c r="O59">
+        <v>12.35090164</v>
+      </c>
+      <c r="P59">
+        <v>43.78956036</v>
+      </c>
+      <c r="Q59">
+        <v>-24.71043964</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1155066875522339</v>
+      </c>
+      <c r="T59">
+        <v>1.667536685918129</v>
+      </c>
+      <c r="U59">
+        <v>0.0509</v>
+      </c>
+      <c r="V59">
+        <v>0.22</v>
+      </c>
+      <c r="W59">
+        <v>0.039702</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>5.542278360242915</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.07222406683151682</v>
+      </c>
+      <c r="C60">
+        <v>193.8643874059908</v>
+      </c>
+      <c r="D60">
+        <v>428.8443874059907</v>
+      </c>
+      <c r="E60">
+        <v>247.08</v>
+      </c>
+      <c r="F60">
+        <v>247.08</v>
+      </c>
+      <c r="G60">
+        <v>12.1</v>
+      </c>
+      <c r="H60">
+        <v>426</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>-68.5</v>
+      </c>
+      <c r="L60">
+        <v>68.5</v>
+      </c>
+      <c r="M60">
+        <v>12.576372</v>
+      </c>
+      <c r="N60">
+        <v>55.923628</v>
+      </c>
+      <c r="O60">
+        <v>12.30319816</v>
+      </c>
+      <c r="P60">
+        <v>43.62042984</v>
+      </c>
+      <c r="Q60">
+        <v>-24.87957016</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1171354924559924</v>
+      </c>
+      <c r="T60">
+        <v>1.702945488173748</v>
+      </c>
+      <c r="U60">
+        <v>0.0509</v>
+      </c>
+      <c r="V60">
+        <v>0.22</v>
+      </c>
+      <c r="W60">
+        <v>0.039702</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>5.446721836790451</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.07215011801557306</v>
+      </c>
+      <c r="C61">
+        <v>189.8715187627554</v>
+      </c>
+      <c r="D61">
+        <v>429.1115187627554</v>
+      </c>
+      <c r="E61">
+        <v>251.34</v>
+      </c>
+      <c r="F61">
+        <v>251.34</v>
+      </c>
+      <c r="G61">
+        <v>12.1</v>
+      </c>
+      <c r="H61">
+        <v>426</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>-68.5</v>
+      </c>
+      <c r="L61">
+        <v>68.5</v>
+      </c>
+      <c r="M61">
+        <v>12.793206</v>
+      </c>
+      <c r="N61">
+        <v>55.706794</v>
+      </c>
+      <c r="O61">
+        <v>12.25549468</v>
+      </c>
+      <c r="P61">
+        <v>43.45129932</v>
+      </c>
+      <c r="Q61">
+        <v>-25.04870068</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1188437512574953</v>
+      </c>
+      <c r="T61">
+        <v>1.740081549075984</v>
+      </c>
+      <c r="U61">
+        <v>0.0509</v>
+      </c>
+      <c r="V61">
+        <v>0.22</v>
+      </c>
+      <c r="W61">
+        <v>0.039702</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>5.354404517522816</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.07207616919962931</v>
+      </c>
+      <c r="C62">
+        <v>185.8789831244136</v>
+      </c>
+      <c r="D62">
+        <v>429.3789831244135</v>
+      </c>
+      <c r="E62">
+        <v>255.6</v>
+      </c>
+      <c r="F62">
+        <v>255.6</v>
+      </c>
+      <c r="G62">
+        <v>12.1</v>
+      </c>
+      <c r="H62">
+        <v>426</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>-68.5</v>
+      </c>
+      <c r="L62">
+        <v>68.5</v>
+      </c>
+      <c r="M62">
+        <v>13.01004</v>
+      </c>
+      <c r="N62">
+        <v>55.48996</v>
+      </c>
+      <c r="O62">
+        <v>12.2077912</v>
+      </c>
+      <c r="P62">
+        <v>43.28216879999999</v>
+      </c>
+      <c r="Q62">
+        <v>-25.21783120000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1206374229990732</v>
+      </c>
+      <c r="T62">
+        <v>1.779074413023331</v>
+      </c>
+      <c r="U62">
+        <v>0.0509</v>
+      </c>
+      <c r="V62">
+        <v>0.22</v>
+      </c>
+      <c r="W62">
+        <v>0.039702</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.265164442230769</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.07200222038368553</v>
+      </c>
+      <c r="C63">
+        <v>181.8867811140376</v>
+      </c>
+      <c r="D63">
+        <v>429.6467811140376</v>
+      </c>
+      <c r="E63">
+        <v>259.86</v>
+      </c>
+      <c r="F63">
+        <v>259.86</v>
+      </c>
+      <c r="G63">
+        <v>12.1</v>
+      </c>
+      <c r="H63">
+        <v>426</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>-68.5</v>
+      </c>
+      <c r="L63">
+        <v>68.5</v>
+      </c>
+      <c r="M63">
+        <v>13.226874</v>
+      </c>
+      <c r="N63">
+        <v>55.273126</v>
+      </c>
+      <c r="O63">
+        <v>12.16008772</v>
+      </c>
+      <c r="P63">
+        <v>43.11303828</v>
+      </c>
+      <c r="Q63">
+        <v>-25.38696172</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.122523077906886</v>
+      </c>
+      <c r="T63">
+        <v>1.82006691101926</v>
+      </c>
+      <c r="U63">
+        <v>0.0509</v>
+      </c>
+      <c r="V63">
+        <v>0.22</v>
+      </c>
+      <c r="W63">
+        <v>0.039702</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.178850271046658</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.07192827156774177</v>
+      </c>
+      <c r="C64">
+        <v>177.894913356255</v>
+      </c>
+      <c r="D64">
+        <v>429.914913356255</v>
+      </c>
+      <c r="E64">
+        <v>264.12</v>
+      </c>
+      <c r="F64">
+        <v>264.12</v>
+      </c>
+      <c r="G64">
+        <v>12.1</v>
+      </c>
+      <c r="H64">
+        <v>426</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>-68.5</v>
+      </c>
+      <c r="L64">
+        <v>68.5</v>
+      </c>
+      <c r="M64">
+        <v>13.443708</v>
+      </c>
+      <c r="N64">
+        <v>55.056292</v>
+      </c>
+      <c r="O64">
+        <v>12.11238424</v>
+      </c>
+      <c r="P64">
+        <v>42.94390776</v>
+      </c>
+      <c r="Q64">
+        <v>-25.55609224</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1245079778098468</v>
+      </c>
+      <c r="T64">
+        <v>1.863216908909713</v>
+      </c>
+      <c r="U64">
+        <v>0.0509</v>
+      </c>
+      <c r="V64">
+        <v>0.22</v>
+      </c>
+      <c r="W64">
+        <v>0.039702</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.095320427965261</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.07185432275179801</v>
+      </c>
+      <c r="C65">
+        <v>173.9033804772537</v>
+      </c>
+      <c r="D65">
+        <v>430.1833804772536</v>
+      </c>
+      <c r="E65">
+        <v>268.38</v>
+      </c>
+      <c r="F65">
+        <v>268.38</v>
+      </c>
+      <c r="G65">
+        <v>12.1</v>
+      </c>
+      <c r="H65">
+        <v>426</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>-68.5</v>
+      </c>
+      <c r="L65">
+        <v>68.5</v>
+      </c>
+      <c r="M65">
+        <v>13.660542</v>
+      </c>
+      <c r="N65">
+        <v>54.839458</v>
+      </c>
+      <c r="O65">
+        <v>12.06468076</v>
+      </c>
+      <c r="P65">
+        <v>42.77477724</v>
+      </c>
+      <c r="Q65">
+        <v>-25.72522276</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1266001695994541</v>
+      </c>
+      <c r="T65">
+        <v>1.908699339118567</v>
+      </c>
+      <c r="U65">
+        <v>0.0509</v>
+      </c>
+      <c r="V65">
+        <v>0.22</v>
+      </c>
+      <c r="W65">
+        <v>0.039702</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.014442325934066</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.07178037393585425</v>
+      </c>
+      <c r="C66">
+        <v>169.9121831047866</v>
+      </c>
+      <c r="D66">
+        <v>430.4521831047866</v>
+      </c>
+      <c r="E66">
+        <v>272.64</v>
+      </c>
+      <c r="F66">
+        <v>272.64</v>
+      </c>
+      <c r="G66">
+        <v>12.1</v>
+      </c>
+      <c r="H66">
+        <v>426</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>-68.5</v>
+      </c>
+      <c r="L66">
+        <v>68.5</v>
+      </c>
+      <c r="M66">
+        <v>13.877376</v>
+      </c>
+      <c r="N66">
+        <v>54.622624</v>
+      </c>
+      <c r="O66">
+        <v>12.01697728</v>
+      </c>
+      <c r="P66">
+        <v>42.60564672</v>
+      </c>
+      <c r="Q66">
+        <v>-25.89435328</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1288085942662618</v>
+      </c>
+      <c r="T66">
+        <v>1.956708571005692</v>
+      </c>
+      <c r="U66">
+        <v>0.0509</v>
+      </c>
+      <c r="V66">
+        <v>0.22</v>
+      </c>
+      <c r="W66">
+        <v>0.039702</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>4.936091664591347</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.0717064251199105</v>
+      </c>
+      <c r="C67">
+        <v>165.9213218681767</v>
+      </c>
+      <c r="D67">
+        <v>430.7213218681767</v>
+      </c>
+      <c r="E67">
+        <v>276.9</v>
+      </c>
+      <c r="F67">
+        <v>276.9</v>
+      </c>
+      <c r="G67">
+        <v>12.1</v>
+      </c>
+      <c r="H67">
+        <v>426</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>-68.5</v>
+      </c>
+      <c r="L67">
+        <v>68.5</v>
+      </c>
+      <c r="M67">
+        <v>14.09421</v>
+      </c>
+      <c r="N67">
+        <v>54.40579</v>
+      </c>
+      <c r="O67">
+        <v>11.9692738</v>
+      </c>
+      <c r="P67">
+        <v>42.4365162</v>
+      </c>
+      <c r="Q67">
+        <v>-26.0634838</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1311432146283157</v>
+      </c>
+      <c r="T67">
+        <v>2.007461187572081</v>
+      </c>
+      <c r="U67">
+        <v>0.0509</v>
+      </c>
+      <c r="V67">
+        <v>0.22</v>
+      </c>
+      <c r="W67">
+        <v>0.039702</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>4.860151792828402</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.07163247630396674</v>
+      </c>
+      <c r="C68">
+        <v>161.9307973983218</v>
+      </c>
+      <c r="D68">
+        <v>430.9907973983218</v>
+      </c>
+      <c r="E68">
+        <v>281.16</v>
+      </c>
+      <c r="F68">
+        <v>281.16</v>
+      </c>
+      <c r="G68">
+        <v>12.1</v>
+      </c>
+      <c r="H68">
+        <v>426</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>-68.5</v>
+      </c>
+      <c r="L68">
+        <v>68.5</v>
+      </c>
+      <c r="M68">
+        <v>14.311044</v>
+      </c>
+      <c r="N68">
+        <v>54.188956</v>
+      </c>
+      <c r="O68">
+        <v>11.92157032</v>
+      </c>
+      <c r="P68">
+        <v>42.26738568</v>
+      </c>
+      <c r="Q68">
+        <v>-26.23261432</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1336151655999022</v>
+      </c>
+      <c r="T68">
+        <v>2.061199252171786</v>
+      </c>
+      <c r="U68">
+        <v>0.0509</v>
+      </c>
+      <c r="V68">
+        <v>0.22</v>
+      </c>
+      <c r="W68">
+        <v>0.039702</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>4.786513129300699</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.07155852748802298</v>
+      </c>
+      <c r="C69">
+        <v>157.9406103276996</v>
+      </c>
+      <c r="D69">
+        <v>431.2606103276996</v>
+      </c>
+      <c r="E69">
+        <v>285.42</v>
+      </c>
+      <c r="F69">
+        <v>285.42</v>
+      </c>
+      <c r="G69">
+        <v>12.1</v>
+      </c>
+      <c r="H69">
+        <v>426</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>-68.5</v>
+      </c>
+      <c r="L69">
+        <v>68.5</v>
+      </c>
+      <c r="M69">
+        <v>14.527878</v>
+      </c>
+      <c r="N69">
+        <v>53.972122</v>
+      </c>
+      <c r="O69">
+        <v>11.87386684</v>
+      </c>
+      <c r="P69">
+        <v>42.09825516</v>
+      </c>
+      <c r="Q69">
+        <v>-26.40174484</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1362369317818878</v>
+      </c>
+      <c r="T69">
+        <v>2.118194169171474</v>
+      </c>
+      <c r="U69">
+        <v>0.0509</v>
+      </c>
+      <c r="V69">
+        <v>0.22</v>
+      </c>
+      <c r="W69">
+        <v>0.039702</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>4.715072634833525</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.07148457867207922</v>
+      </c>
+      <c r="C70">
+        <v>153.9507612903728</v>
+      </c>
+      <c r="D70">
+        <v>431.5307612903728</v>
+      </c>
+      <c r="E70">
+        <v>289.68</v>
+      </c>
+      <c r="F70">
+        <v>289.68</v>
+      </c>
+      <c r="G70">
+        <v>12.1</v>
+      </c>
+      <c r="H70">
+        <v>426</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>-68.5</v>
+      </c>
+      <c r="L70">
+        <v>68.5</v>
+      </c>
+      <c r="M70">
+        <v>14.744712</v>
+      </c>
+      <c r="N70">
+        <v>53.755288</v>
+      </c>
+      <c r="O70">
+        <v>11.82616336</v>
+      </c>
+      <c r="P70">
+        <v>41.92912464</v>
+      </c>
+      <c r="Q70">
+        <v>-26.57087536</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1390225583502476</v>
+      </c>
+      <c r="T70">
+        <v>2.178751268483643</v>
+      </c>
+      <c r="U70">
+        <v>0.0509</v>
+      </c>
+      <c r="V70">
+        <v>0.22</v>
+      </c>
+      <c r="W70">
+        <v>0.039702</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>4.645733331380091</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.07141062985613546</v>
+      </c>
+      <c r="C71">
+        <v>149.9612509219934</v>
+      </c>
+      <c r="D71">
+        <v>431.8012509219934</v>
+      </c>
+      <c r="E71">
+        <v>293.94</v>
+      </c>
+      <c r="F71">
+        <v>293.94</v>
+      </c>
+      <c r="G71">
+        <v>12.1</v>
+      </c>
+      <c r="H71">
+        <v>426</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>-68.5</v>
+      </c>
+      <c r="L71">
+        <v>68.5</v>
+      </c>
+      <c r="M71">
+        <v>14.961546</v>
+      </c>
+      <c r="N71">
+        <v>53.538454</v>
+      </c>
+      <c r="O71">
+        <v>11.77845988</v>
+      </c>
+      <c r="P71">
+        <v>41.75999412</v>
+      </c>
+      <c r="Q71">
+        <v>-26.74000588</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1419879027617273</v>
+      </c>
+      <c r="T71">
+        <v>2.243215277428854</v>
+      </c>
+      <c r="U71">
+        <v>0.0509</v>
+      </c>
+      <c r="V71">
+        <v>0.22</v>
+      </c>
+      <c r="W71">
+        <v>0.039702</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>4.578403862809365</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.07133668104019168</v>
+      </c>
+      <c r="C72">
+        <v>145.9720798598087</v>
+      </c>
+      <c r="D72">
+        <v>432.0720798598088</v>
+      </c>
+      <c r="E72">
+        <v>298.2</v>
+      </c>
+      <c r="F72">
+        <v>298.2</v>
+      </c>
+      <c r="G72">
+        <v>12.1</v>
+      </c>
+      <c r="H72">
+        <v>426</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>-68.5</v>
+      </c>
+      <c r="L72">
+        <v>68.5</v>
+      </c>
+      <c r="M72">
+        <v>15.17838</v>
+      </c>
+      <c r="N72">
+        <v>53.32162</v>
+      </c>
+      <c r="O72">
+        <v>11.7307564</v>
+      </c>
+      <c r="P72">
+        <v>41.5908636</v>
+      </c>
+      <c r="Q72">
+        <v>-26.9091364</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.145150936800639</v>
+      </c>
+      <c r="T72">
+        <v>2.311976886970412</v>
+      </c>
+      <c r="U72">
+        <v>0.0509</v>
+      </c>
+      <c r="V72">
+        <v>0.22</v>
+      </c>
+      <c r="W72">
+        <v>0.039702</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>4.512998093340659</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.07270261222424793</v>
+      </c>
+      <c r="C73">
+        <v>136.7637067000606</v>
+      </c>
+      <c r="D73">
+        <v>427.1237067000606</v>
+      </c>
+      <c r="E73">
+        <v>302.46</v>
+      </c>
+      <c r="F73">
+        <v>302.46</v>
+      </c>
+      <c r="G73">
+        <v>12.1</v>
+      </c>
+      <c r="H73">
+        <v>426</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>-68.5</v>
+      </c>
+      <c r="L73">
+        <v>68.5</v>
+      </c>
+      <c r="M73">
+        <v>16.18161</v>
+      </c>
+      <c r="N73">
+        <v>52.31839</v>
+      </c>
+      <c r="O73">
+        <v>11.5100458</v>
+      </c>
+      <c r="P73">
+        <v>40.8083442</v>
+      </c>
+      <c r="Q73">
+        <v>-27.6916558</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1485321111180963</v>
+      </c>
+      <c r="T73">
+        <v>2.385480676480354</v>
+      </c>
+      <c r="U73">
+        <v>0.0535</v>
+      </c>
+      <c r="V73">
+        <v>0.22</v>
+      </c>
+      <c r="W73">
+        <v>0.04173</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>4.233200528253987</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.07264894340830418</v>
+      </c>
+      <c r="C74">
+        <v>132.6959931052639</v>
+      </c>
+      <c r="D74">
+        <v>427.3159931052638</v>
+      </c>
+      <c r="E74">
+        <v>306.72</v>
+      </c>
+      <c r="F74">
+        <v>306.72</v>
+      </c>
+      <c r="G74">
+        <v>12.1</v>
+      </c>
+      <c r="H74">
+        <v>426</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>-68.5</v>
+      </c>
+      <c r="L74">
+        <v>68.5</v>
+      </c>
+      <c r="M74">
+        <v>16.40952</v>
+      </c>
+      <c r="N74">
+        <v>52.09048</v>
+      </c>
+      <c r="O74">
+        <v>11.4599056</v>
+      </c>
+      <c r="P74">
+        <v>40.6305744</v>
+      </c>
+      <c r="Q74">
+        <v>-27.8694256</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1521547978868006</v>
+      </c>
+      <c r="T74">
+        <v>2.464234736669578</v>
+      </c>
+      <c r="U74">
+        <v>0.0535</v>
+      </c>
+      <c r="V74">
+        <v>0.22</v>
+      </c>
+      <c r="W74">
+        <v>0.04173</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.174406076472682</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.0725952745923604</v>
+      </c>
+      <c r="C75">
+        <v>128.6284527189024</v>
+      </c>
+      <c r="D75">
+        <v>427.5084527189024</v>
+      </c>
+      <c r="E75">
+        <v>310.98</v>
+      </c>
+      <c r="F75">
+        <v>310.98</v>
+      </c>
+      <c r="G75">
+        <v>12.1</v>
+      </c>
+      <c r="H75">
+        <v>426</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>-68.5</v>
+      </c>
+      <c r="L75">
+        <v>68.5</v>
+      </c>
+      <c r="M75">
+        <v>16.63743</v>
+      </c>
+      <c r="N75">
+        <v>51.86257</v>
+      </c>
+      <c r="O75">
+        <v>11.4097654</v>
+      </c>
+      <c r="P75">
+        <v>40.4528046</v>
+      </c>
+      <c r="Q75">
+        <v>-28.0471954</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1560458318235571</v>
+      </c>
+      <c r="T75">
+        <v>2.548822430946892</v>
+      </c>
+      <c r="U75">
+        <v>0.0535</v>
+      </c>
+      <c r="V75">
+        <v>0.22</v>
+      </c>
+      <c r="W75">
+        <v>0.04173</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.117222431589494</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.07254160577641665</v>
+      </c>
+      <c r="C76">
+        <v>124.5610857751165</v>
+      </c>
+      <c r="D76">
+        <v>427.7010857751165</v>
+      </c>
+      <c r="E76">
+        <v>315.24</v>
+      </c>
+      <c r="F76">
+        <v>315.24</v>
+      </c>
+      <c r="G76">
+        <v>12.1</v>
+      </c>
+      <c r="H76">
+        <v>426</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>-68.5</v>
+      </c>
+      <c r="L76">
+        <v>68.5</v>
+      </c>
+      <c r="M76">
+        <v>16.86534</v>
+      </c>
+      <c r="N76">
+        <v>51.63466</v>
+      </c>
+      <c r="O76">
+        <v>11.3596252</v>
+      </c>
+      <c r="P76">
+        <v>40.2750348</v>
+      </c>
+      <c r="Q76">
+        <v>-28.2249652</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1602361760631409</v>
+      </c>
+      <c r="T76">
+        <v>2.639916870937846</v>
+      </c>
+      <c r="U76">
+        <v>0.0535</v>
+      </c>
+      <c r="V76">
+        <v>0.22</v>
+      </c>
+      <c r="W76">
+        <v>0.04173</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.061584290622068</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.07248793696047288</v>
+      </c>
+      <c r="C77">
+        <v>120.493892508469</v>
+      </c>
+      <c r="D77">
+        <v>427.893892508469</v>
+      </c>
+      <c r="E77">
+        <v>319.5</v>
+      </c>
+      <c r="F77">
+        <v>319.5</v>
+      </c>
+      <c r="G77">
+        <v>12.1</v>
+      </c>
+      <c r="H77">
+        <v>426</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>-68.5</v>
+      </c>
+      <c r="L77">
+        <v>68.5</v>
+      </c>
+      <c r="M77">
+        <v>17.09325</v>
+      </c>
+      <c r="N77">
+        <v>51.40675</v>
+      </c>
+      <c r="O77">
+        <v>11.309485</v>
+      </c>
+      <c r="P77">
+        <v>40.097265</v>
+      </c>
+      <c r="Q77">
+        <v>-28.402735</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1647617478418915</v>
+      </c>
+      <c r="T77">
+        <v>2.738298866128077</v>
+      </c>
+      <c r="U77">
+        <v>0.0535</v>
+      </c>
+      <c r="V77">
+        <v>0.22</v>
+      </c>
+      <c r="W77">
+        <v>0.04173</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.007429833413775</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.07403482814452914</v>
+      </c>
+      <c r="C78">
+        <v>110.745450150082</v>
+      </c>
+      <c r="D78">
+        <v>422.4054501500819</v>
+      </c>
+      <c r="E78">
+        <v>323.76</v>
+      </c>
+      <c r="F78">
+        <v>323.76</v>
+      </c>
+      <c r="G78">
+        <v>12.1</v>
+      </c>
+      <c r="H78">
+        <v>426</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>-68.5</v>
+      </c>
+      <c r="L78">
+        <v>68.5</v>
+      </c>
+      <c r="M78">
+        <v>18.195312</v>
+      </c>
+      <c r="N78">
+        <v>50.304688</v>
+      </c>
+      <c r="O78">
+        <v>11.06703136</v>
+      </c>
+      <c r="P78">
+        <v>39.23765664</v>
+      </c>
+      <c r="Q78">
+        <v>-29.26234336</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1696644506022047</v>
+      </c>
+      <c r="T78">
+        <v>2.844879360917493</v>
+      </c>
+      <c r="U78">
+        <v>0.0562</v>
+      </c>
+      <c r="V78">
+        <v>0.22</v>
+      </c>
+      <c r="W78">
+        <v>0.043836</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>3.764705985805575</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.07400221932858536</v>
+      </c>
+      <c r="C79">
+        <v>106.5996946345157</v>
+      </c>
+      <c r="D79">
+        <v>422.5196946345157</v>
+      </c>
+      <c r="E79">
+        <v>328.02</v>
+      </c>
+      <c r="F79">
+        <v>328.02</v>
+      </c>
+      <c r="G79">
+        <v>12.1</v>
+      </c>
+      <c r="H79">
+        <v>426</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>-68.5</v>
+      </c>
+      <c r="L79">
+        <v>68.5</v>
+      </c>
+      <c r="M79">
+        <v>18.434724</v>
+      </c>
+      <c r="N79">
+        <v>50.065276</v>
+      </c>
+      <c r="O79">
+        <v>11.01436072</v>
+      </c>
+      <c r="P79">
+        <v>39.05091528</v>
+      </c>
+      <c r="Q79">
+        <v>-29.44908472</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1749934753416755</v>
+      </c>
+      <c r="T79">
+        <v>2.960727724819033</v>
+      </c>
+      <c r="U79">
+        <v>0.0562</v>
+      </c>
+      <c r="V79">
+        <v>0.22</v>
+      </c>
+      <c r="W79">
+        <v>0.043836</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>3.715813700275632</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.0739696105126416</v>
+      </c>
+      <c r="C80">
+        <v>102.4540009331765</v>
+      </c>
+      <c r="D80">
+        <v>422.6340009331765</v>
+      </c>
+      <c r="E80">
+        <v>332.28</v>
+      </c>
+      <c r="F80">
+        <v>332.28</v>
+      </c>
+      <c r="G80">
+        <v>12.1</v>
+      </c>
+      <c r="H80">
+        <v>426</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>-68.5</v>
+      </c>
+      <c r="L80">
+        <v>68.5</v>
+      </c>
+      <c r="M80">
+        <v>18.674136</v>
+      </c>
+      <c r="N80">
+        <v>49.825864</v>
+      </c>
+      <c r="O80">
+        <v>10.96169008</v>
+      </c>
+      <c r="P80">
+        <v>38.86417392</v>
+      </c>
+      <c r="Q80">
+        <v>-29.63582608</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1808069568756437</v>
+      </c>
+      <c r="T80">
+        <v>3.087107758166167</v>
+      </c>
+      <c r="U80">
+        <v>0.0562</v>
+      </c>
+      <c r="V80">
+        <v>0.22</v>
+      </c>
+      <c r="W80">
+        <v>0.043836</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>3.668175063092611</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.07393700169669784</v>
+      </c>
+      <c r="C81">
+        <v>98.30836909624645</v>
+      </c>
+      <c r="D81">
+        <v>422.7483690962464</v>
+      </c>
+      <c r="E81">
+        <v>336.54</v>
+      </c>
+      <c r="F81">
+        <v>336.54</v>
+      </c>
+      <c r="G81">
+        <v>12.1</v>
+      </c>
+      <c r="H81">
+        <v>426</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>-68.5</v>
+      </c>
+      <c r="L81">
+        <v>68.5</v>
+      </c>
+      <c r="M81">
+        <v>18.913548</v>
+      </c>
+      <c r="N81">
+        <v>49.58645199999999</v>
+      </c>
+      <c r="O81">
+        <v>10.90901944</v>
+      </c>
+      <c r="P81">
+        <v>38.67743256</v>
+      </c>
+      <c r="Q81">
+        <v>-29.82256744</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1871741033176088</v>
+      </c>
+      <c r="T81">
+        <v>3.225523985165409</v>
+      </c>
+      <c r="U81">
+        <v>0.0562</v>
+      </c>
+      <c r="V81">
+        <v>0.22</v>
+      </c>
+      <c r="W81">
+        <v>0.043836</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>3.621742467357261</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.07390439288075408</v>
+      </c>
+      <c r="C82">
+        <v>94.16279917396241</v>
+      </c>
+      <c r="D82">
+        <v>422.8627991739624</v>
+      </c>
+      <c r="E82">
+        <v>340.8</v>
+      </c>
+      <c r="F82">
+        <v>340.8</v>
+      </c>
+      <c r="G82">
+        <v>12.1</v>
+      </c>
+      <c r="H82">
+        <v>426</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>-68.5</v>
+      </c>
+      <c r="L82">
+        <v>68.5</v>
+      </c>
+      <c r="M82">
+        <v>19.15296</v>
+      </c>
+      <c r="N82">
+        <v>49.34704</v>
+      </c>
+      <c r="O82">
+        <v>10.8563488</v>
+      </c>
+      <c r="P82">
+        <v>38.4906912</v>
+      </c>
+      <c r="Q82">
+        <v>-30.0093088</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.1941779644037704</v>
+      </c>
+      <c r="T82">
+        <v>3.377781834864575</v>
+      </c>
+      <c r="U82">
+        <v>0.0562</v>
+      </c>
+      <c r="V82">
+        <v>0.22</v>
+      </c>
+      <c r="W82">
+        <v>0.043836</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>3.576470686515296</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.07387178406481032</v>
+      </c>
+      <c r="C83">
+        <v>90.01729121661526</v>
+      </c>
+      <c r="D83">
+        <v>422.9772912166152</v>
+      </c>
+      <c r="E83">
+        <v>345.06</v>
+      </c>
+      <c r="F83">
+        <v>345.06</v>
+      </c>
+      <c r="G83">
+        <v>12.1</v>
+      </c>
+      <c r="H83">
+        <v>426</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>-68.5</v>
+      </c>
+      <c r="L83">
+        <v>68.5</v>
+      </c>
+      <c r="M83">
+        <v>19.392372</v>
+      </c>
+      <c r="N83">
+        <v>49.107628</v>
+      </c>
+      <c r="O83">
+        <v>10.80367816</v>
+      </c>
+      <c r="P83">
+        <v>38.30394984</v>
+      </c>
+      <c r="Q83">
+        <v>-30.19605016</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2019190740253175</v>
+      </c>
+      <c r="T83">
+        <v>3.546066826637337</v>
+      </c>
+      <c r="U83">
+        <v>0.0562</v>
+      </c>
+      <c r="V83">
+        <v>0.22</v>
+      </c>
+      <c r="W83">
+        <v>0.043836</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>3.532316727422514</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.07684529524886655</v>
+      </c>
+      <c r="C84">
+        <v>75.56585989414947</v>
+      </c>
+      <c r="D84">
+        <v>412.7858598941495</v>
+      </c>
+      <c r="E84">
+        <v>349.3200000000001</v>
+      </c>
+      <c r="F84">
+        <v>349.3200000000001</v>
+      </c>
+      <c r="G84">
+        <v>12.1</v>
+      </c>
+      <c r="H84">
+        <v>426</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>-68.5</v>
+      </c>
+      <c r="L84">
+        <v>68.5</v>
+      </c>
+      <c r="M84">
+        <v>21.273588</v>
+      </c>
+      <c r="N84">
+        <v>47.226412</v>
+      </c>
+      <c r="O84">
+        <v>10.38981064</v>
+      </c>
+      <c r="P84">
+        <v>36.83660136</v>
+      </c>
+      <c r="Q84">
+        <v>-31.66339864</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2105203069381476</v>
+      </c>
+      <c r="T84">
+        <v>3.733050150829295</v>
+      </c>
+      <c r="U84">
+        <v>0.0609</v>
+      </c>
+      <c r="V84">
+        <v>0.22</v>
+      </c>
+      <c r="W84">
+        <v>0.047502</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>3.219955185744877</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.07684934643292279</v>
+      </c>
+      <c r="C85">
+        <v>71.29230983831599</v>
+      </c>
+      <c r="D85">
+        <v>412.772309838316</v>
+      </c>
+      <c r="E85">
+        <v>353.58</v>
+      </c>
+      <c r="F85">
+        <v>353.58</v>
+      </c>
+      <c r="G85">
+        <v>12.1</v>
+      </c>
+      <c r="H85">
+        <v>426</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>-68.5</v>
+      </c>
+      <c r="L85">
+        <v>68.5</v>
+      </c>
+      <c r="M85">
+        <v>21.533022</v>
+      </c>
+      <c r="N85">
+        <v>46.966978</v>
+      </c>
+      <c r="O85">
+        <v>10.33273516</v>
+      </c>
+      <c r="P85">
+        <v>36.63424284</v>
+      </c>
+      <c r="Q85">
+        <v>-31.86575716</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2201334496054283</v>
+      </c>
+      <c r="T85">
+        <v>3.942031513161485</v>
+      </c>
+      <c r="U85">
+        <v>0.0609</v>
+      </c>
+      <c r="V85">
+        <v>0.22</v>
+      </c>
+      <c r="W85">
+        <v>0.047502</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>3.18116054495277</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.07685339761697904</v>
+      </c>
+      <c r="C86">
+        <v>67.01876067203824</v>
+      </c>
+      <c r="D86">
+        <v>412.7587606720382</v>
+      </c>
+      <c r="E86">
+        <v>357.84</v>
+      </c>
+      <c r="F86">
+        <v>357.84</v>
+      </c>
+      <c r="G86">
+        <v>12.1</v>
+      </c>
+      <c r="H86">
+        <v>426</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>-68.5</v>
+      </c>
+      <c r="L86">
+        <v>68.5</v>
+      </c>
+      <c r="M86">
+        <v>21.792456</v>
+      </c>
+      <c r="N86">
+        <v>46.707544</v>
+      </c>
+      <c r="O86">
+        <v>10.27565968</v>
+      </c>
+      <c r="P86">
+        <v>36.43188431999999</v>
+      </c>
+      <c r="Q86">
+        <v>-32.06811568000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2309482351061189</v>
+      </c>
+      <c r="T86">
+        <v>4.177135545785195</v>
+      </c>
+      <c r="U86">
+        <v>0.0609</v>
+      </c>
+      <c r="V86">
+        <v>0.22</v>
+      </c>
+      <c r="W86">
+        <v>0.047502</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>3.143289586084285</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.07685744880103529</v>
+      </c>
+      <c r="C87">
+        <v>62.74521239522835</v>
+      </c>
+      <c r="D87">
+        <v>412.7452123952283</v>
+      </c>
+      <c r="E87">
+        <v>362.1</v>
+      </c>
+      <c r="F87">
+        <v>362.1</v>
+      </c>
+      <c r="G87">
+        <v>12.1</v>
+      </c>
+      <c r="H87">
+        <v>426</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>-68.5</v>
+      </c>
+      <c r="L87">
+        <v>68.5</v>
+      </c>
+      <c r="M87">
+        <v>22.05189</v>
+      </c>
+      <c r="N87">
+        <v>46.44811</v>
+      </c>
+      <c r="O87">
+        <v>10.2185842</v>
+      </c>
+      <c r="P87">
+        <v>36.2295258</v>
+      </c>
+      <c r="Q87">
+        <v>-32.2704742</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2432049920069018</v>
+      </c>
+      <c r="T87">
+        <v>4.443586782758736</v>
+      </c>
+      <c r="U87">
+        <v>0.0609</v>
+      </c>
+      <c r="V87">
+        <v>0.22</v>
+      </c>
+      <c r="W87">
+        <v>0.047502</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>3.106309708600941</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.07686149998509151</v>
+      </c>
+      <c r="C88">
+        <v>58.471665007799</v>
+      </c>
+      <c r="D88">
+        <v>412.731665007799</v>
+      </c>
+      <c r="E88">
+        <v>366.36</v>
+      </c>
+      <c r="F88">
+        <v>366.36</v>
+      </c>
+      <c r="G88">
+        <v>12.1</v>
+      </c>
+      <c r="H88">
+        <v>426</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>-68.5</v>
+      </c>
+      <c r="L88">
+        <v>68.5</v>
+      </c>
+      <c r="M88">
+        <v>22.311324</v>
+      </c>
+      <c r="N88">
+        <v>46.188676</v>
+      </c>
+      <c r="O88">
+        <v>10.16150872</v>
+      </c>
+      <c r="P88">
+        <v>36.02716728</v>
+      </c>
+      <c r="Q88">
+        <v>-32.47283272</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2572127141792251</v>
+      </c>
+      <c r="T88">
+        <v>4.748102482157067</v>
+      </c>
+      <c r="U88">
+        <v>0.0609</v>
+      </c>
+      <c r="V88">
+        <v>0.22</v>
+      </c>
+      <c r="W88">
+        <v>0.047502</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>3.070189828268372</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.07686555116914776</v>
+      </c>
+      <c r="C89">
+        <v>54.19811850966238</v>
+      </c>
+      <c r="D89">
+        <v>412.7181185096624</v>
+      </c>
+      <c r="E89">
+        <v>370.62</v>
+      </c>
+      <c r="F89">
+        <v>370.62</v>
+      </c>
+      <c r="G89">
+        <v>12.1</v>
+      </c>
+      <c r="H89">
+        <v>426</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>-68.5</v>
+      </c>
+      <c r="L89">
+        <v>68.5</v>
+      </c>
+      <c r="M89">
+        <v>22.570758</v>
+      </c>
+      <c r="N89">
+        <v>45.929242</v>
+      </c>
+      <c r="O89">
+        <v>10.10443324</v>
+      </c>
+      <c r="P89">
+        <v>35.82480876</v>
+      </c>
+      <c r="Q89">
+        <v>-32.67519124</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2733754705319058</v>
+      </c>
+      <c r="T89">
+        <v>5.099466750693604</v>
+      </c>
+      <c r="U89">
+        <v>0.0609</v>
+      </c>
+      <c r="V89">
+        <v>0.22</v>
+      </c>
+      <c r="W89">
+        <v>0.047502</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>3.034900290012414</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.076869602353204</v>
+      </c>
+      <c r="C90">
+        <v>49.92457290073111</v>
+      </c>
+      <c r="D90">
+        <v>412.7045729007311</v>
+      </c>
+      <c r="E90">
+        <v>374.88</v>
+      </c>
+      <c r="F90">
+        <v>374.88</v>
+      </c>
+      <c r="G90">
+        <v>12.1</v>
+      </c>
+      <c r="H90">
+        <v>426</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>-68.5</v>
+      </c>
+      <c r="L90">
+        <v>68.5</v>
+      </c>
+      <c r="M90">
+        <v>22.830192</v>
+      </c>
+      <c r="N90">
+        <v>45.669808</v>
+      </c>
+      <c r="O90">
+        <v>10.04735776</v>
+      </c>
+      <c r="P90">
+        <v>35.62245024000001</v>
+      </c>
+      <c r="Q90">
+        <v>-32.87754975999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.2922320196100333</v>
+      </c>
+      <c r="T90">
+        <v>5.509391730652898</v>
+      </c>
+      <c r="U90">
+        <v>0.0609</v>
+      </c>
+      <c r="V90">
+        <v>0.22</v>
+      </c>
+      <c r="W90">
+        <v>0.047502</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.000412786716818</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.08332971353726024</v>
+      </c>
+      <c r="C91">
+        <v>25.13935645994491</v>
+      </c>
+      <c r="D91">
+        <v>392.1793564599449</v>
+      </c>
+      <c r="E91">
+        <v>379.14</v>
+      </c>
+      <c r="F91">
+        <v>379.14</v>
+      </c>
+      <c r="G91">
+        <v>12.1</v>
+      </c>
+      <c r="H91">
+        <v>426</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>-68.5</v>
+      </c>
+      <c r="L91">
+        <v>68.5</v>
+      </c>
+      <c r="M91">
+        <v>26.615628</v>
+      </c>
+      <c r="N91">
+        <v>41.884372</v>
+      </c>
+      <c r="O91">
+        <v>9.21456184</v>
+      </c>
+      <c r="P91">
+        <v>32.66981016</v>
+      </c>
+      <c r="Q91">
+        <v>-35.83018984</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3145170321569112</v>
+      </c>
+      <c r="T91">
+        <v>5.993848525150244</v>
+      </c>
+      <c r="U91">
+        <v>0.0702</v>
+      </c>
+      <c r="V91">
+        <v>0.22</v>
+      </c>
+      <c r="W91">
+        <v>0.054756</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>2.573675886963855</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.08340630472131647</v>
+      </c>
+      <c r="C92">
+        <v>20.64824792590321</v>
+      </c>
+      <c r="D92">
+        <v>391.9482479259032</v>
+      </c>
+      <c r="E92">
+        <v>383.4</v>
+      </c>
+      <c r="F92">
+        <v>383.4</v>
+      </c>
+      <c r="G92">
+        <v>12.1</v>
+      </c>
+      <c r="H92">
+        <v>426</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>-68.5</v>
+      </c>
+      <c r="L92">
+        <v>68.5</v>
+      </c>
+      <c r="M92">
+        <v>26.91468</v>
+      </c>
+      <c r="N92">
+        <v>41.58532</v>
+      </c>
+      <c r="O92">
+        <v>9.148770399999998</v>
+      </c>
+      <c r="P92">
+        <v>32.4365496</v>
+      </c>
+      <c r="Q92">
+        <v>-36.0634504</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3412590472131647</v>
+      </c>
+      <c r="T92">
+        <v>6.57519667854706</v>
+      </c>
+      <c r="U92">
+        <v>0.0702</v>
+      </c>
+      <c r="V92">
+        <v>0.22</v>
+      </c>
+      <c r="W92">
+        <v>0.054756</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>2.545079488219812</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.08348289590537271</v>
+      </c>
+      <c r="C93">
+        <v>16.15741161270813</v>
+      </c>
+      <c r="D93">
+        <v>391.7174116127081</v>
+      </c>
+      <c r="E93">
+        <v>387.66</v>
+      </c>
+      <c r="F93">
+        <v>387.66</v>
+      </c>
+      <c r="G93">
+        <v>12.1</v>
+      </c>
+      <c r="H93">
+        <v>426</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>-68.5</v>
+      </c>
+      <c r="L93">
+        <v>68.5</v>
+      </c>
+      <c r="M93">
+        <v>27.213732</v>
+      </c>
+      <c r="N93">
+        <v>41.286268</v>
+      </c>
+      <c r="O93">
+        <v>9.08297896</v>
+      </c>
+      <c r="P93">
+        <v>32.20328904</v>
+      </c>
+      <c r="Q93">
+        <v>-36.29671096</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.3739437322819191</v>
+      </c>
+      <c r="T93">
+        <v>7.285733310476503</v>
+      </c>
+      <c r="U93">
+        <v>0.0702</v>
+      </c>
+      <c r="V93">
+        <v>0.22</v>
+      </c>
+      <c r="W93">
+        <v>0.054756</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>2.517111581755858</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.08693220708942895</v>
+      </c>
+      <c r="C94">
+        <v>1.776187941527382</v>
+      </c>
+      <c r="D94">
+        <v>381.5961879415274</v>
+      </c>
+      <c r="E94">
+        <v>391.92</v>
+      </c>
+      <c r="F94">
+        <v>391.92</v>
+      </c>
+      <c r="G94">
+        <v>12.1</v>
+      </c>
+      <c r="H94">
+        <v>426</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>-68.5</v>
+      </c>
+      <c r="L94">
+        <v>68.5</v>
+      </c>
+      <c r="M94">
+        <v>29.354808</v>
+      </c>
+      <c r="N94">
+        <v>39.145192</v>
+      </c>
+      <c r="O94">
+        <v>8.611942240000001</v>
+      </c>
+      <c r="P94">
+        <v>30.53324976</v>
+      </c>
+      <c r="Q94">
+        <v>-37.96675024</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4147995886178621</v>
+      </c>
+      <c r="T94">
+        <v>8.173904100388306</v>
+      </c>
+      <c r="U94">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V94">
+        <v>0.22</v>
+      </c>
+      <c r="W94">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>2.333518924736282</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.08704545827348519</v>
+      </c>
+      <c r="C95">
+        <v>-2.807261402744643</v>
+      </c>
+      <c r="D95">
+        <v>381.2727385972553</v>
+      </c>
+      <c r="E95">
+        <v>396.18</v>
+      </c>
+      <c r="F95">
+        <v>396.18</v>
+      </c>
+      <c r="G95">
+        <v>12.1</v>
+      </c>
+      <c r="H95">
+        <v>426</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>-68.5</v>
+      </c>
+      <c r="L95">
+        <v>68.5</v>
+      </c>
+      <c r="M95">
+        <v>29.673882</v>
+      </c>
+      <c r="N95">
+        <v>38.826118</v>
+      </c>
+      <c r="O95">
+        <v>8.54174596</v>
+      </c>
+      <c r="P95">
+        <v>30.28437204</v>
+      </c>
+      <c r="Q95">
+        <v>-38.21562796</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.4673285467640744</v>
+      </c>
+      <c r="T95">
+        <v>9.315837973132052</v>
+      </c>
+      <c r="U95">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V95">
+        <v>0.22</v>
+      </c>
+      <c r="W95">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>2.308427323395032</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.08715870945754142</v>
+      </c>
+      <c r="C96">
+        <v>-7.390162885801317</v>
+      </c>
+      <c r="D96">
+        <v>380.9498371141987</v>
+      </c>
+      <c r="E96">
+        <v>400.44</v>
+      </c>
+      <c r="F96">
+        <v>400.44</v>
+      </c>
+      <c r="G96">
+        <v>12.1</v>
+      </c>
+      <c r="H96">
+        <v>426</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>-68.5</v>
+      </c>
+      <c r="L96">
+        <v>68.5</v>
+      </c>
+      <c r="M96">
+        <v>29.992956</v>
+      </c>
+      <c r="N96">
+        <v>38.50704400000001</v>
+      </c>
+      <c r="O96">
+        <v>8.471549680000003</v>
+      </c>
+      <c r="P96">
+        <v>30.03549432000001</v>
+      </c>
+      <c r="Q96">
+        <v>-38.46450567999999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.5373671576256909</v>
+      </c>
+      <c r="T96">
+        <v>10.83841647012372</v>
+      </c>
+      <c r="U96">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V96">
+        <v>0.22</v>
+      </c>
+      <c r="W96">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>2.283869585912106</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.08727196064159767</v>
+      </c>
+      <c r="C97">
+        <v>-11.97251789842289</v>
+      </c>
+      <c r="D97">
+        <v>380.6274821015771</v>
+      </c>
+      <c r="E97">
+        <v>404.7</v>
+      </c>
+      <c r="F97">
+        <v>404.7</v>
+      </c>
+      <c r="G97">
+        <v>12.1</v>
+      </c>
+      <c r="H97">
+        <v>426</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>-68.5</v>
+      </c>
+      <c r="L97">
+        <v>68.5</v>
+      </c>
+      <c r="M97">
+        <v>30.31203</v>
+      </c>
+      <c r="N97">
+        <v>38.18797</v>
+      </c>
+      <c r="O97">
+        <v>8.4013534</v>
+      </c>
+      <c r="P97">
+        <v>29.7866166</v>
+      </c>
+      <c r="Q97">
+        <v>-38.7133834</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.6354212128319543</v>
+      </c>
+      <c r="T97">
+        <v>12.97002636591205</v>
+      </c>
+      <c r="U97">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V97">
+        <v>0.22</v>
+      </c>
+      <c r="W97">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>2.25982885342882</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.0873852118256539</v>
+      </c>
+      <c r="C98">
+        <v>-16.55432782668561</v>
+      </c>
+      <c r="D98">
+        <v>380.3056721733143</v>
+      </c>
+      <c r="E98">
+        <v>408.96</v>
+      </c>
+      <c r="F98">
+        <v>408.96</v>
+      </c>
+      <c r="G98">
+        <v>12.1</v>
+      </c>
+      <c r="H98">
+        <v>426</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>-68.5</v>
+      </c>
+      <c r="L98">
+        <v>68.5</v>
+      </c>
+      <c r="M98">
+        <v>30.631104</v>
+      </c>
+      <c r="N98">
+        <v>37.86889600000001</v>
+      </c>
+      <c r="O98">
+        <v>8.331157120000002</v>
+      </c>
+      <c r="P98">
+        <v>29.53773888000001</v>
+      </c>
+      <c r="Q98">
+        <v>-38.96226111999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.782502295641347</v>
+      </c>
+      <c r="T98">
+        <v>16.1674412095945</v>
+      </c>
+      <c r="U98">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V98">
+        <v>0.22</v>
+      </c>
+      <c r="W98">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>2.236288969538937</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.08749846300971013</v>
+      </c>
+      <c r="C99">
+        <v>-21.13559405198271</v>
+      </c>
+      <c r="D99">
+        <v>379.9844059480172</v>
+      </c>
+      <c r="E99">
+        <v>413.22</v>
+      </c>
+      <c r="F99">
+        <v>413.22</v>
+      </c>
+      <c r="G99">
+        <v>12.1</v>
+      </c>
+      <c r="H99">
+        <v>426</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>-68.5</v>
+      </c>
+      <c r="L99">
+        <v>68.5</v>
+      </c>
+      <c r="M99">
+        <v>30.95017799999999</v>
+      </c>
+      <c r="N99">
+        <v>37.54982200000001</v>
+      </c>
+      <c r="O99">
+        <v>8.260960840000001</v>
+      </c>
+      <c r="P99">
+        <v>29.28886116</v>
+      </c>
+      <c r="Q99">
+        <v>-39.21113884</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.027637433657004</v>
+      </c>
+      <c r="T99">
+        <v>21.49646594906531</v>
+      </c>
+      <c r="U99">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V99">
+        <v>0.22</v>
+      </c>
+      <c r="W99">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>2.213234444079773</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.08761171419376639</v>
+      </c>
+      <c r="C100">
+        <v>-25.71631795104338</v>
+      </c>
+      <c r="D100">
+        <v>379.6636820489566</v>
+      </c>
+      <c r="E100">
+        <v>417.48</v>
+      </c>
+      <c r="F100">
+        <v>417.48</v>
+      </c>
+      <c r="G100">
+        <v>12.1</v>
+      </c>
+      <c r="H100">
+        <v>426</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>-68.5</v>
+      </c>
+      <c r="L100">
+        <v>68.5</v>
+      </c>
+      <c r="M100">
+        <v>31.269252</v>
+      </c>
+      <c r="N100">
+        <v>37.23074800000001</v>
+      </c>
+      <c r="O100">
+        <v>8.190764560000002</v>
+      </c>
+      <c r="P100">
+        <v>29.03998344</v>
+      </c>
+      <c r="Q100">
+        <v>-39.46001656</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.517907709688318</v>
+      </c>
+      <c r="T100">
+        <v>32.15451542800692</v>
+      </c>
+      <c r="U100">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V100">
+        <v>0.22</v>
+      </c>
+      <c r="W100">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>2.190650419140183</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.08772496537782262</v>
+      </c>
+      <c r="C101">
+        <v>-30.29650089595236</v>
+      </c>
+      <c r="D101">
+        <v>379.3434991040476</v>
+      </c>
+      <c r="E101">
+        <v>421.74</v>
+      </c>
+      <c r="F101">
+        <v>421.74</v>
+      </c>
+      <c r="G101">
+        <v>12.1</v>
+      </c>
+      <c r="H101">
+        <v>426</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>-68.5</v>
+      </c>
+      <c r="L101">
+        <v>68.5</v>
+      </c>
+      <c r="M101">
+        <v>31.588326</v>
+      </c>
+      <c r="N101">
+        <v>36.911674</v>
+      </c>
+      <c r="O101">
+        <v>8.120568280000001</v>
+      </c>
+      <c r="P101">
+        <v>28.79110572</v>
+      </c>
+      <c r="Q101">
+        <v>-39.70889428</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>2.98871853778226</v>
+      </c>
+      <c r="T101">
+        <v>64.12866386483174</v>
+      </c>
+      <c r="U101">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V101">
+        <v>0.22</v>
+      </c>
+      <c r="W101">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>2.168522637128666</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
